--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6502000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6203000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5944000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5659000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5109000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4132000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3281000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2975000</v>
       </c>
       <c r="L8" s="3">
         <v>2975000</v>
       </c>
       <c r="M8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="N8" s="3">
         <v>2701000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2483000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2576000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2676000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2855000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3200000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3334000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3503000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3497000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3428000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3348000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3222000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3085000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -951,8 +957,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1052,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1277,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,8 +1372,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1445,8 +1467,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3331000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2914000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2580000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2309000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1833000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>898000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>266000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-98000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-214000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-84000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>422000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-416000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>152000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>192000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>328000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>689000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1067000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1182000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1179000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1142000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>970000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>815000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>724000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>649000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>612000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>586000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>522000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>457000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>384000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3171000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3289000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3364000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3350000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3276000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3234000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3015000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3012000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3189000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3059000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2279000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2899000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2424000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2484000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2527000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2511000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2267000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2321000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2318000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2286000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2378000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2407000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2361000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,192 +1726,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2116000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1430000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1589000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1303000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-964000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-702000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-670000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-786000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-929000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-885000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-894000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-992000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-763000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-746000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-701000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1098000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1908000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1835000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2112000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1945000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2086000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1980000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2113000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2221000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2234000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1734000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2572000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2307000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1930000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-518000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1207000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1749000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1761000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1731000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1566000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1905000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1933000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1947000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,192 +2009,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1859000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1775000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2047000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1881000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2028000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1836000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1728000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1663000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1813000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1315000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2197000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1754000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1698000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-902000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>879000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1338000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1436000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1424000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1294000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1615000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1661000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1660000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E24" s="3">
         <v>289000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>275000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>353000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>333000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>388000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>340000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>299000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>357000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>323000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>212000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>371000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>298000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>166000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-158000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>120000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>195000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>255000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>239000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>212000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>264000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>261000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>304000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>253000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>183000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>413000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>386000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>320000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>319000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>883000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1570000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1500000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1694000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1548000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1640000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1496000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1429000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1306000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1490000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1103000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1826000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1456000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1532000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-744000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>759000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1143000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1181000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1185000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1082000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1351000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1400000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1356000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>891000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>740000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1440000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1347000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1599000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1401000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1550000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1402000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1355000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1214000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1408000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1037000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1750000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1387000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1447000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-807000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>684000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1061000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1093000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1109000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>999000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1276000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1285000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>815000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>967000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>975000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2579,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2548,8 +2608,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
@@ -2560,32 +2620,32 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
         <v>4399000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>156000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>238000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>211000</v>
-      </c>
-      <c r="U29" s="3">
-        <v>189000</v>
       </c>
       <c r="V29" s="3">
         <v>189000</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>189000</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2596,12 +2656,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2614,8 +2674,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2116000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1430000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1589000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1303000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1395000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1206000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1179000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1284000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1526000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1246000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>964000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>702000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>670000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>786000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3429000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1632000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>929000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>885000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>894000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>992000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>763000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>746000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>701000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>775000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>669000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>670000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>668000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>705000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>740000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1440000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1347000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1599000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1401000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1550000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1402000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1355000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1214000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1408000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1037000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1750000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1387000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1447000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3592000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>840000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1299000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1304000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1298000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1188000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1276000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1285000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>967000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>975000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>740000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1440000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1347000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1599000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1401000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1550000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1402000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1355000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1214000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1408000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1037000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1750000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1387000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1447000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3592000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>840000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1299000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1304000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1298000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1188000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1276000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1285000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>967000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>975000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,192 +3416,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6921000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5300000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6191000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5940000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7043000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6548000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8582000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7572000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8004000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8843000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8724000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7455000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7017000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6629000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6338000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7493000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5061000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5671000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5416000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5062000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5608000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5248000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5425000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>43804000</v>
+      </c>
+      <c r="E42" s="3">
         <v>41484000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>38259000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>33865000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27320000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>40278000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28404000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48776000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>74250000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>75478000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72447000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>86161000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>85173000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>70959000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>50233000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>19986000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>23413000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>19036000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>18362000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>15261000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>10893000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>19800000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>21972000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3607,8 +3699,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3699,8 +3794,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3791,8 +3889,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3883,100 +3984,106 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8314000</v>
+      </c>
+      <c r="E47" s="3">
         <v>8046000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8015000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8323000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8437000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8130000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8441000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7798000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8180000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7737000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7521000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6386000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6052000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4938000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4943000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13205000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13734000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13325000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13001000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12567000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12894000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12446000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12430000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4010,23 +4117,23 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>1876000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
-        <v>2000000</v>
+      <c r="S48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T48" s="3">
         <v>2000000</v>
@@ -4035,11 +4142,11 @@
         <v>2000000</v>
       </c>
       <c r="V48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="W48" s="3">
         <v>2144000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4049,8 +4156,8 @@
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -4067,100 +4174,106 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14618000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14993000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14442000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14280000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14410000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14193000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13524000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13124000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12734000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12718000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12751000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10997000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10475000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10346000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10300000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10315000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10877000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10716000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10848000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11030000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11201000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11354000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11263000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,8 +4459,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4435,8 +4554,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>561580000</v>
+      </c>
+      <c r="E54" s="3">
         <v>557334000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>558207000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>561777000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>557263000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>559477000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>540786000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>541246000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>557191000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>553515000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>554212000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>474414000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>466679000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>461817000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>458978000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>445493000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>410295000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>408916000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>405761000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>392837000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>382315000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>380080000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>380711000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,8 +4816,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4779,8 +4909,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4871,100 +5004,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15621000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17437000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15325000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14376000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15762000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19245000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15622000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14623000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12741000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14199000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11186000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11931000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9514000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10629000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12345000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17150000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11831000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12220000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13804000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12793000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9002000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9851000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9340000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5055,100 +5194,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34737000</v>
+      </c>
+      <c r="E61" s="3">
         <v>30167000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31384000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28802000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26638000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24558000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25984000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26571000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30784000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>33471000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>34813000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31530000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>33695000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36610000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>38526000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>49908000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>43922000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>39453000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>39649000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>39468000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>35918000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37919000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37186000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5239,8 +5384,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>510475000</v>
+      </c>
+      <c r="E66" s="3">
         <v>507880000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>508887000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>512733000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>511489000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>512789000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>493134000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>492065000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>501496000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>497256000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>499585000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>420565000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>412669000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>408541000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>406055000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>396230000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>360981000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>359496000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>356421000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>344301000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>334587000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>333022000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>333807000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +5989,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56290000</v>
+      </c>
+      <c r="E72" s="3">
         <v>56170000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>55346000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>54598000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53572000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>52777000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51841000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51058000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50228000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49541000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48663000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48113000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>46848000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>45947000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>44986000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41885000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>42215000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>41413000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>40616000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39742000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38919000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38080000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37201000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51105000</v>
+      </c>
+      <c r="E76" s="3">
         <v>49454000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49320000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49044000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45774000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46688000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47652000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49181000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>55695000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>56259000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>54627000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53849000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>54010000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53276000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52923000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49263000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49314000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49420000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49340000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>48536000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>47728000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47058000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>46904000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>740000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1440000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1347000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1599000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1401000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1550000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1402000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1355000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1214000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1408000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1037000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1750000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1387000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1447000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3592000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>840000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1299000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1304000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1298000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1188000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1276000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1285000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>967000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>975000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +6981,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E83" s="3">
         <v>49000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>60000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>65000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>58000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>144000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>385000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>558000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>421000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>419000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>375000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>553000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>232000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>384000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>328000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>411000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>325000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>307000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>272000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>290000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>272000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>287000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>280000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>258000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>291000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>289000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>279000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>276000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4864000</v>
+      </c>
+      <c r="E89" s="3">
         <v>115000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3256000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1876000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4046000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3394000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2632000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-989000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3494000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1525000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1415000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>780000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1935000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>393000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3027000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-696000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3115000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>604000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2243000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1401000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2137000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1164000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1617000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>873000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>675000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,8 +7681,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7554,8 +7774,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4665000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1688000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2310000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12707000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3312000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>9022000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>805000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>851000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>162000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,8 +8096,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7873,91 +8106,94 @@
         <v>-624000</v>
       </c>
       <c r="E96" s="3">
+        <v>-624000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-606000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-607000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-612000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-622000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-626000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-531000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-533000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-538000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-492000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-493000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-492000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-494000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-491000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-503000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-509000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-518000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-432000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-436000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-442000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-446000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-355000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,100 +8474,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1422000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2733000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-796000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>16262000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>68000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4724000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5730000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5196000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3040000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13676000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>26507000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>540000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2893000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9571000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4076000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>538000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>368000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8416,96 +8664,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1621000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-891000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>251000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>495000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1010000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-432000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-839000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>119000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1269000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>438000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>388000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>291000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2432000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-610000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>255000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>354000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-546000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>360000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-177000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>776000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>513000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>36000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>124000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>348000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,217 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6500000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6502000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6203000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5944000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5659000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5109000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4132000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3281000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2975000</v>
       </c>
       <c r="M8" s="3">
         <v>2975000</v>
       </c>
       <c r="N8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="O8" s="3">
         <v>2701000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2483000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2576000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2676000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2855000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3200000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3334000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3503000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3497000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3428000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3348000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3222000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -960,8 +966,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1055,8 +1064,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,8 +1394,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1470,8 +1492,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3391000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3331000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2914000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2580000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2309000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1833000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>898000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>266000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-98000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-214000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-84000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>422000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-416000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>152000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>192000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>328000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>689000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1067000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1182000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1179000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1142000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>970000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>815000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>724000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>649000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>612000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>586000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>522000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>457000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>384000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3109000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3171000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3289000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3364000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3350000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3276000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3234000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3015000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3012000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3189000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3059000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2279000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2899000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2424000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2484000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2527000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2511000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2267000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2321000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2318000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2286000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2378000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2407000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,198 +1759,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1453000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2116000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1430000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1589000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1303000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-964000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-702000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-670000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-786000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-929000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-885000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-894000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-992000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-763000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-746000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1693000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1098000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1908000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1835000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2112000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1945000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2086000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1980000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2113000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2221000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2234000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1734000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2572000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2307000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1930000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-518000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1207000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1749000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1761000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1731000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1566000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1905000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1933000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2012,198 +2051,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1055000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1859000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1775000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2047000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1881000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2028000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1836000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1728000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1663000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1813000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1315000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2197000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1754000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1698000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-902000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>879000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1338000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1436000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1424000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1294000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1615000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1661000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E24" s="3">
         <v>172000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>289000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>275000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>353000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>333000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>388000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>340000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>299000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>357000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>323000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>212000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>371000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>298000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>166000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-158000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>120000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>195000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>255000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>239000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>212000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>264000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>261000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>304000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>253000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>183000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>413000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>386000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>320000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>319000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1344000</v>
+      </c>
+      <c r="E26" s="3">
         <v>883000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1570000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1694000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1548000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1640000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1496000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1429000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1306000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1490000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1103000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1826000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1456000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1532000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-744000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>759000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1143000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1181000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1185000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1082000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1351000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1400000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>891000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="E27" s="3">
         <v>740000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1440000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1347000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1599000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1401000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1550000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1402000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1355000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1214000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1408000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1037000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1750000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1387000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1447000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-807000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>684000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1061000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1093000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1109000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>999000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1276000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1319000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>815000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>967000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>975000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,8 +2639,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2611,8 +2671,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
@@ -2623,32 +2683,32 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
         <v>4399000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>156000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>238000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>211000</v>
-      </c>
-      <c r="V29" s="3">
-        <v>189000</v>
       </c>
       <c r="W29" s="3">
         <v>189000</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>189000</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2659,12 +2719,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2677,8 +2737,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1453000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2116000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1430000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1589000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1303000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1395000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1206000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1179000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1284000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1526000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1246000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>964000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>702000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>670000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>786000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3429000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1632000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>929000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>885000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>894000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>992000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>763000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>746000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>701000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>775000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>669000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>670000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>668000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>705000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="E33" s="3">
         <v>740000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1440000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1347000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1599000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1401000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1550000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1402000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1355000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1214000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1408000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1037000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1750000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1387000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1447000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3592000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>840000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1299000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1304000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1298000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1188000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1276000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1319000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>967000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>975000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="E35" s="3">
         <v>740000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1440000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1347000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1599000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1401000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1550000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1402000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1355000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1214000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1408000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1037000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1750000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1387000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1447000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3592000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>840000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1299000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1304000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1298000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1188000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1276000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1319000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>967000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>975000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,198 +3502,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5933000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6921000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5300000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6191000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5940000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7043000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6548000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8582000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7572000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8004000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8843000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8724000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7455000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7017000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6629000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6338000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7493000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5061000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5671000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5416000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5062000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5608000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5248000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>53612000</v>
+      </c>
+      <c r="E42" s="3">
         <v>43804000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>41484000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>38259000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>33865000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27320000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>40278000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>28404000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>48776000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>74250000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>75478000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>72447000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>86161000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>85173000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>70959000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>50233000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>19986000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>23413000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19036000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>18362000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>15261000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>10893000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>19800000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3702,8 +3794,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3797,8 +3892,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3892,8 +3990,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3987,103 +4088,109 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8280000</v>
+      </c>
+      <c r="E47" s="3">
         <v>8314000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8046000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8015000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8323000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8437000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8130000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8441000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7798000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8180000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7737000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7521000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6386000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6052000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4938000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4943000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13205000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13734000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13325000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13001000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12567000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12894000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12446000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4120,23 +4227,23 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1876000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
-        <v>2000000</v>
+      <c r="T48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U48" s="3">
         <v>2000000</v>
@@ -4145,11 +4252,11 @@
         <v>2000000</v>
       </c>
       <c r="W48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="X48" s="3">
         <v>2144000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4159,8 +4266,8 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -4177,103 +4284,109 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14694000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14618000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14993000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14442000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14280000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14410000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14193000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13524000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13124000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12734000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12718000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12751000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10997000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10475000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10346000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10300000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10315000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10877000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10716000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10848000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11030000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11201000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11354000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,8 +4578,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4557,8 +4676,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>566162000</v>
+      </c>
+      <c r="E54" s="3">
         <v>561580000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>557334000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>558207000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>561777000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>557263000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>559477000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>540786000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>541246000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>557191000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>553515000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>554212000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>474414000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>466679000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>461817000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>458978000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>445493000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>410295000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>408916000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>405761000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>392837000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>382315000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>380080000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,8 +4946,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4912,8 +5042,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5007,103 +5140,109 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15785000</v>
+      </c>
+      <c r="E59" s="3">
         <v>15621000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17437000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15325000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14376000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15762000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19245000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15622000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14623000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12741000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14199000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11186000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11931000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9514000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10629000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12345000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17150000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11831000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12220000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13804000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12793000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9002000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9851000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5197,103 +5336,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35707000</v>
+      </c>
+      <c r="E61" s="3">
         <v>34737000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30167000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31384000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28802000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26638000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24558000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25984000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26571000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30784000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>33471000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>34813000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31530000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33695000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>36610000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>38526000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>49908000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>43922000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>39453000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>39649000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>39468000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>35918000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37919000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5387,8 +5532,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>514822000</v>
+      </c>
+      <c r="E66" s="3">
         <v>510475000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>507880000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>508887000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>512733000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>511489000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>512789000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>493134000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>492065000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>501496000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>497256000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>499585000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>420565000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>412669000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>408541000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>406055000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>396230000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>360981000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>359496000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>356421000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>344301000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>334587000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>333022000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56913000</v>
+      </c>
+      <c r="E72" s="3">
         <v>56290000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>56170000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>55346000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>54598000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53572000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52777000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51841000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51058000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50228000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49541000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48663000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48113000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46848000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>45947000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>44986000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>41885000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42215000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41413000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>40616000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>39742000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38919000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38080000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51340000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51105000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49454000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49320000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49044000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45774000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46688000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47652000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49181000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>55695000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>56259000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>54627000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53849000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>54010000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53276000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>52923000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49263000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49314000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49420000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>49340000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>48536000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47728000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47058000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="E81" s="3">
         <v>740000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1440000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1347000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1599000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1401000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1550000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1402000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1355000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1214000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1408000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1037000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1750000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1387000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1447000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3592000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>840000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1299000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1304000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1298000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1188000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1276000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1319000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>967000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>975000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,103 +7179,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E83" s="3">
         <v>43000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>65000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>64000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>58000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>144000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>385000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>558000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>421000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>419000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>375000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>553000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>232000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>384000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>328000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>411000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>325000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>307000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>272000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>290000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>272000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>287000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>280000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>258000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>291000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>289000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>279000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>276000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1758000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4864000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>115000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3256000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1876000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4046000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3394000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2632000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-989000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3494000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1525000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1415000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>780000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1935000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>393000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3027000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-696000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3115000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>604000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2243000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1401000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2137000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1164000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>873000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>675000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,8 +7901,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7777,8 +7997,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6365000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4665000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1688000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2310000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12707000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3312000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9022000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>805000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>851000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>162000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,8 +8329,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8109,91 +8342,94 @@
         <v>-624000</v>
       </c>
       <c r="F96" s="3">
+        <v>-624000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-606000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-607000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-612000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-622000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-626000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-531000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-533000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-538000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-492000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-493000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-492000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-494000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-491000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-503000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-509000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-518000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-432000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-436000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-442000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-446000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,103 +8719,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3619000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1422000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2733000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-796000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>16262000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>68000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4724000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5730000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5196000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3040000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13676000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>26507000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>540000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2893000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>9571000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4076000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>538000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>368000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8667,99 +8915,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-988000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1621000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-891000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>251000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>495000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1010000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-432000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-839000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>119000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1269000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>438000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>388000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>291000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2432000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-610000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>255000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>354000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-546000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>360000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-177000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>776000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>513000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>36000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>124000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>348000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,223 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6568000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6500000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6502000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6203000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5944000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5659000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5109000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4132000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3281000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2975000</v>
       </c>
       <c r="N8" s="3">
         <v>2975000</v>
       </c>
       <c r="O8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="P8" s="3">
         <v>2701000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2483000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2576000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2676000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2855000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3200000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3334000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3503000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3497000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3428000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3348000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -969,8 +975,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,8 +1076,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1315,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1416,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1495,8 +1517,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3501000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3391000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3331000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2914000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2580000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2309000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1833000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>898000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>266000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-98000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-214000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-84000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>422000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-416000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>152000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>192000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>328000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>689000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1067000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1182000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1179000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1142000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>970000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>815000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>724000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>649000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>612000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>586000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>522000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>457000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>384000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3067000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3109000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3171000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3289000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3364000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3350000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3276000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3234000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3015000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3012000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3189000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3059000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2279000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2899000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2424000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2484000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2527000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2511000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2267000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2321000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2318000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2286000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2378000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,204 +1792,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1248000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1453000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2116000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1430000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1589000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1303000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-964000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-702000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-670000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-786000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-929000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-885000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-894000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-992000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-763000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1856000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1693000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1098000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1908000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1835000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2112000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1945000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2086000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1980000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2113000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2221000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2234000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1734000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2572000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2307000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1930000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-518000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1207000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1749000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1761000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1731000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1566000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1905000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2054,204 +2093,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1819000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1656000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1055000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1859000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1775000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2047000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1881000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2028000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1836000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1728000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1663000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1813000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1315000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2197000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1754000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1698000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-902000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>879000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1338000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1436000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1424000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1294000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E24" s="3">
         <v>312000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>172000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>289000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>275000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>353000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>333000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>388000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>340000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>299000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>357000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>323000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>212000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>371000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>298000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>166000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-158000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>120000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>195000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>255000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>239000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>212000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>264000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>261000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>304000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>253000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>183000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>413000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>386000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>320000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>319000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1477000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1344000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>883000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1570000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1500000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1694000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1548000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1640000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1496000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1429000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1306000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1490000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1103000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1826000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1456000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1532000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-744000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>759000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1143000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1181000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1185000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1082000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1351000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>891000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1355000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1240000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>740000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1440000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1347000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1599000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1401000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1550000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1402000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1355000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1214000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1408000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1037000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1750000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1387000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1447000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-807000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>684000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1061000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1093000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1109000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>999000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1276000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>815000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>967000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>975000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2674,8 +2734,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
@@ -2686,32 +2746,32 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>4399000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>156000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>238000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>211000</v>
-      </c>
-      <c r="W29" s="3">
-        <v>189000</v>
       </c>
       <c r="X29" s="3">
         <v>189000</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>189000</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2722,12 +2782,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1248000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1453000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2116000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1430000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1589000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1303000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1395000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1206000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1179000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1284000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1526000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1246000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>964000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>702000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>670000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>786000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3429000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1632000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>929000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>885000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>894000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>992000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>763000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>746000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>701000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>775000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>669000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>670000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>668000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>705000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1355000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1240000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>740000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1440000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1347000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1599000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1401000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1550000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1402000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1355000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1214000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1408000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1037000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1750000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1387000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1447000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3592000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>840000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1299000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1304000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1298000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1188000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1276000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>967000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>975000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1355000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1240000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>740000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1440000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1347000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1599000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1401000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1550000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1402000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1355000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1214000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1408000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1037000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1750000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1387000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1447000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3592000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>840000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1299000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1304000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1298000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1188000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1276000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>967000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>975000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,204 +3588,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6242000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5933000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6921000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5300000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6191000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5940000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7043000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6548000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8582000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7572000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8004000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8843000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8724000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7455000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7017000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6629000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6338000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7493000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5061000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5671000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5416000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5062000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5608000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>33039000</v>
+      </c>
+      <c r="E42" s="3">
         <v>53612000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>43804000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>41484000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>38259000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>33865000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>27320000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>40278000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>28404000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>48776000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>74250000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>75478000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72447000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>86161000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>85173000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>70959000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>50233000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>19986000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>23413000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>19036000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18362000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>15261000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10893000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3797,8 +3889,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3895,8 +3990,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3993,8 +4091,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4091,106 +4192,112 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9037000</v>
+      </c>
+      <c r="E47" s="3">
         <v>8280000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8314000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8046000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8015000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8323000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8437000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8130000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8441000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7798000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8180000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7737000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7521000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6386000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6052000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4938000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4943000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13205000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13734000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13325000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13001000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12567000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12894000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4230,23 +4337,23 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>1876000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
-        <v>2000000</v>
+      <c r="U48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V48" s="3">
         <v>2000000</v>
@@ -4255,11 +4362,11 @@
         <v>2000000</v>
       </c>
       <c r="X48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="Y48" s="3">
         <v>2144000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4269,8 +4376,8 @@
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -4287,106 +4394,112 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14671000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14694000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14618000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14993000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14442000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14280000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14410000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14193000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13524000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13124000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12734000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12718000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12751000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10997000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10475000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10346000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10300000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10315000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10877000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10716000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10848000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11030000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11201000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,8 +4697,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4679,8 +4798,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>556519000</v>
+      </c>
+      <c r="E54" s="3">
         <v>566162000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>561580000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>557334000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>558207000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>561777000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>557263000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>559477000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>540786000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>541246000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>557191000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>553515000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>554212000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>474414000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>466679000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>461817000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>458978000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>445493000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>410295000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>408916000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>405761000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>392837000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>382315000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,8 +5076,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5045,8 +5175,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5143,106 +5276,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15339000</v>
+      </c>
+      <c r="E59" s="3">
         <v>15785000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15621000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17437000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15325000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14376000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15762000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19245000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15622000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14623000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12741000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14199000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11186000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11931000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9514000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10629000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12345000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17150000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11831000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12220000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13804000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12793000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9002000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5339,106 +5478,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36391000</v>
+      </c>
+      <c r="E61" s="3">
         <v>35707000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>34737000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>30167000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31384000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28802000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26638000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24558000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25984000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26571000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30784000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>33471000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>34813000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31530000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>33695000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>36610000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>38526000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>49908000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43922000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>39453000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>39649000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>39468000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35918000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5535,8 +5680,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>503877000</v>
+      </c>
+      <c r="E66" s="3">
         <v>514822000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>510475000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>507880000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>508887000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>512733000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>511489000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>512789000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>493134000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>492065000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>501496000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>497256000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>499585000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>420565000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>412669000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>408541000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>406055000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>396230000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>360981000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>359496000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>356421000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>344301000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>334587000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,8 +6323,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>57652000</v>
+      </c>
+      <c r="E72" s="3">
         <v>56913000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>56290000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56170000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55346000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54598000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53572000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52777000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51841000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51058000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>50228000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>49541000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48663000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>48113000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46848000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>45947000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>44986000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>41885000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>42215000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>41413000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>40616000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39742000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38919000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52642000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51340000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51105000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49454000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49320000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>49044000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45774000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46688000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47652000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49181000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>55695000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>56259000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>54627000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53849000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>54010000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>53276000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52923000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49263000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49314000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>49420000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>49340000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>48536000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47728000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1355000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1240000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>740000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1440000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1347000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1599000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1401000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1550000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1402000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1355000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1214000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1408000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1037000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1750000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1387000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1447000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3592000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>840000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1299000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1304000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1298000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1188000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1276000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>967000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>975000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,8 +7377,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7189,97 +7387,100 @@
         <v>37000</v>
       </c>
       <c r="E83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F83" s="3">
         <v>43000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>60000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>65000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>144000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>385000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>558000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>421000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>419000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>375000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>553000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>232000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>384000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>328000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>411000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>325000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>307000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>272000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>290000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>272000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>287000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>280000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>258000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>291000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>289000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>279000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>276000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1035000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1758000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4864000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>115000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3256000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1876000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4046000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3394000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2632000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-989000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3494000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1525000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1415000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>780000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1935000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>393000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3027000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-696000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3115000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>604000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2243000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1401000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2137000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>873000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>675000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,8 +8121,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8000,8 +8220,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6365000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4665000</v>
       </c>
-      <c r="F94" s="3">
-        <v>1688000</v>
-      </c>
       <c r="G94" s="3">
-        <v>2310000</v>
+        <v>-9251000</v>
       </c>
       <c r="H94" s="3">
+        <v>13249000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12707000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3312000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9022000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>805000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>851000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>162000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,13 +8562,14 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-624000</v>
+        <v>-623000</v>
       </c>
       <c r="E96" s="3">
         <v>-624000</v>
@@ -8345,91 +8578,94 @@
         <v>-624000</v>
       </c>
       <c r="G96" s="3">
+        <v>-624000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-606000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-607000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-612000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-622000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-626000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-531000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-533000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-538000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-492000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-493000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-492000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-494000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-491000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-503000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-509000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-518000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-432000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-436000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-442000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,106 +8964,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11271000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3619000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1422000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2733000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-796000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16262000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>68000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4724000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5730000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5196000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3040000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13676000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>26507000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>540000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2893000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>9571000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4076000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>538000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>368000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8918,102 +9166,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10456000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-988000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1621000</v>
       </c>
-      <c r="F102" s="3">
-        <v>-891000</v>
-      </c>
       <c r="G102" s="3">
-        <v>251000</v>
+        <v>-11830000</v>
       </c>
       <c r="H102" s="3">
+        <v>11190000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>495000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1010000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-432000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-839000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>119000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1269000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>438000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>388000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>291000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2432000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-610000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>255000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>354000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-546000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>360000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>776000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>513000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>36000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>124000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>348000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,229 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6568000</v>
+        <v>5189000</v>
       </c>
       <c r="E8" s="3">
-        <v>6500000</v>
+        <v>5176000</v>
       </c>
       <c r="F8" s="3">
-        <v>6502000</v>
+        <v>4990000</v>
       </c>
       <c r="G8" s="3">
-        <v>6203000</v>
+        <v>5129000</v>
       </c>
       <c r="H8" s="3">
-        <v>5944000</v>
+        <v>5104000</v>
       </c>
       <c r="I8" s="3">
-        <v>5659000</v>
+        <v>5147000</v>
       </c>
       <c r="J8" s="3">
+        <v>5368000</v>
+      </c>
+      <c r="K8" s="3">
         <v>5109000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4132000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3281000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2975000</v>
       </c>
       <c r="O8" s="3">
         <v>2975000</v>
       </c>
       <c r="P8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2701000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2483000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2576000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2676000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2855000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3200000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3334000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3503000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3497000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3428000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3348000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -978,31 +984,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>5189000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5176000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4990000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5129000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5104000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5147000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5368000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1079,8 +1088,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,31 +1334,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1419,31 +1438,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1520,8 +1542,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3501000</v>
+        <v>3327000</v>
       </c>
       <c r="E17" s="3">
-        <v>3391000</v>
+        <v>3357000</v>
       </c>
       <c r="F17" s="3">
-        <v>3331000</v>
+        <v>3334000</v>
       </c>
       <c r="G17" s="3">
-        <v>2914000</v>
+        <v>4074000</v>
       </c>
       <c r="H17" s="3">
-        <v>2580000</v>
+        <v>3245000</v>
       </c>
       <c r="I17" s="3">
-        <v>2309000</v>
+        <v>3372000</v>
       </c>
       <c r="J17" s="3">
+        <v>3321000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1833000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>898000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>266000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-98000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-214000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-84000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>422000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-416000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>152000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>192000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>328000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>689000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1067000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1182000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1179000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1142000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>970000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>815000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>724000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>649000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>612000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>586000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>522000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>457000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>384000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3067000</v>
+        <v>1862000</v>
       </c>
       <c r="E18" s="3">
-        <v>3109000</v>
+        <v>1819000</v>
       </c>
       <c r="F18" s="3">
-        <v>3171000</v>
+        <v>1656000</v>
       </c>
       <c r="G18" s="3">
-        <v>3289000</v>
+        <v>1055000</v>
       </c>
       <c r="H18" s="3">
-        <v>3364000</v>
+        <v>1859000</v>
       </c>
       <c r="I18" s="3">
-        <v>3350000</v>
+        <v>1775000</v>
       </c>
       <c r="J18" s="3">
+        <v>2047000</v>
+      </c>
+      <c r="K18" s="3">
         <v>3276000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3234000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3015000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3012000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3189000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3059000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2279000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2899000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2424000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2484000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2527000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2511000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2267000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2321000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2318000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2286000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2378000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,233 +1825,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-1248000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1453000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2116000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1430000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1589000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1303000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-964000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-702000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-670000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-786000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-929000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-885000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-894000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-992000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-763000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1883000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1856000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1693000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1098000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1908000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1835000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2112000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1945000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2086000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1980000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2113000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2221000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2234000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1734000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2572000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2307000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1930000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-518000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1207000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1749000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1761000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1731000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1566000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1905000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2096,210 +2135,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1862000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1819000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1656000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1055000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1859000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1775000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2047000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1881000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2028000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1836000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1728000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1663000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1813000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1315000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2197000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1754000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1698000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-902000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>879000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1338000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1436000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1424000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1294000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1615000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E24" s="3">
         <v>342000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>312000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>172000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>289000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>275000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>353000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>333000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>388000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>340000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>299000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>357000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>323000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>212000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>371000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>298000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>166000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-158000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>120000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>195000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>255000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>239000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>212000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>264000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>261000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>304000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>253000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>183000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>413000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>386000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>320000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>319000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1505000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1477000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1344000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>883000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1570000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1500000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1694000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1548000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1640000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1496000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1429000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1306000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1490000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1103000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1826000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1456000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1532000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-744000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>759000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1143000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1181000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1185000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1082000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1351000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>891000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1355000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1240000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>740000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1440000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1347000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1599000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1401000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1550000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1402000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1355000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1214000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1408000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1750000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1387000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1447000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-807000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>684000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1061000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1093000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1109000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>999000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1276000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>815000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>967000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>975000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2737,8 +2797,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>5</v>
@@ -2749,32 +2809,32 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>4399000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>156000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>238000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>211000</v>
-      </c>
-      <c r="X29" s="3">
-        <v>189000</v>
       </c>
       <c r="Y29" s="3">
         <v>189000</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>189000</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2785,12 +2845,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>1248000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1453000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2116000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1430000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1589000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1303000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>1395000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1206000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1179000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1284000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1526000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1246000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>964000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>702000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>670000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>786000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3429000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1632000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>929000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>885000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>894000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>992000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>763000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>746000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>701000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>775000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>669000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>670000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>668000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>705000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1490000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1459000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>864000</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1554000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1483000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1677000</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1401000</v>
+      </c>
+      <c r="L33" s="3">
+        <v>1550000</v>
+      </c>
+      <c r="M33" s="3">
+        <v>1402000</v>
+      </c>
+      <c r="N33" s="3">
         <v>1355000</v>
       </c>
-      <c r="E33" s="3">
-        <v>1240000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>740000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1440000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1347000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1599000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1401000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1550000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1402000</v>
-      </c>
-      <c r="M33" s="3">
-        <v>1355000</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1214000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1408000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1750000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1387000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1447000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3592000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>840000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1299000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1304000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1298000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1188000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1276000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>967000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>975000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1490000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1459000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>864000</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1554000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1483000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1677000</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1401000</v>
+      </c>
+      <c r="L35" s="3">
+        <v>1550000</v>
+      </c>
+      <c r="M35" s="3">
+        <v>1402000</v>
+      </c>
+      <c r="N35" s="3">
         <v>1355000</v>
       </c>
-      <c r="E35" s="3">
-        <v>1240000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>740000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1440000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1347000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1599000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1401000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1550000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1402000</v>
-      </c>
-      <c r="M35" s="3">
-        <v>1355000</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1214000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1408000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1750000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1387000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1447000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3592000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>840000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1299000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1304000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1298000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1188000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1276000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>967000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>975000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,233 +3674,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6242000</v>
+        <v>5702000</v>
       </c>
       <c r="E41" s="3">
-        <v>5933000</v>
+        <v>5368000</v>
       </c>
       <c r="F41" s="3">
-        <v>6921000</v>
+        <v>4999000</v>
       </c>
       <c r="G41" s="3">
-        <v>5300000</v>
+        <v>5936000</v>
       </c>
       <c r="H41" s="3">
-        <v>6191000</v>
+        <v>4782000</v>
       </c>
       <c r="I41" s="3">
-        <v>5940000</v>
+        <v>5604000</v>
       </c>
       <c r="J41" s="3">
+        <v>5335000</v>
+      </c>
+      <c r="K41" s="3">
         <v>7043000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6548000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8582000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7572000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8004000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8843000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8724000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7455000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7017000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6629000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6338000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7493000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5061000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5671000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5416000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5062000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5608000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33039000</v>
+        <v>4083000</v>
       </c>
       <c r="E42" s="3">
-        <v>53612000</v>
+        <v>3449000</v>
       </c>
       <c r="F42" s="3">
-        <v>43804000</v>
+        <v>56821000</v>
       </c>
       <c r="G42" s="3">
-        <v>41484000</v>
+        <v>4200000</v>
       </c>
       <c r="H42" s="3">
-        <v>38259000</v>
+        <v>3699000</v>
       </c>
       <c r="I42" s="3">
-        <v>33865000</v>
+        <v>3811000</v>
       </c>
       <c r="J42" s="3">
+        <v>37191000</v>
+      </c>
+      <c r="K42" s="3">
         <v>27320000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>40278000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>28404000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>48776000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>74250000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>75478000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>72447000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>86161000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>85173000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>70959000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>50233000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19986000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>23413000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>19036000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>18362000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>15261000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10893000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3892,31 +3984,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3993,31 +4088,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>1881000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2020000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>1884000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>1925000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1789000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1731000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1692000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4094,31 +4192,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>47931000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>12733000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>65416000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>13816000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>11746000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>12604000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>45859000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4195,132 +4296,138 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9037000</v>
+        <v>153400000</v>
       </c>
       <c r="E47" s="3">
-        <v>8280000</v>
+        <v>147682000</v>
       </c>
       <c r="F47" s="3">
-        <v>8314000</v>
+        <v>138740000</v>
       </c>
       <c r="G47" s="3">
-        <v>8046000</v>
+        <v>140883000</v>
       </c>
       <c r="H47" s="3">
-        <v>8015000</v>
+        <v>140433000</v>
       </c>
       <c r="I47" s="3">
-        <v>8323000</v>
+        <v>143676000</v>
       </c>
       <c r="J47" s="3">
+        <v>146562000</v>
+      </c>
+      <c r="K47" s="3">
         <v>8437000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8130000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8441000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7798000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8180000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7737000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7521000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6386000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6052000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4938000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4943000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13205000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13734000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13325000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13001000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12567000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12894000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>1745000</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4340,23 +4447,23 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>1876000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V48" s="3">
-        <v>2000000</v>
+      <c r="V48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W48" s="3">
         <v>2000000</v>
@@ -4365,11 +4472,11 @@
         <v>2000000</v>
       </c>
       <c r="Y48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>2144000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4379,8 +4486,8 @@
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
@@ -4397,109 +4504,115 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14435000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14671000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14694000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14618000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14993000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14442000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14280000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14410000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14193000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13524000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13124000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12734000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12718000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12751000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10997000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10475000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10346000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10300000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10315000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10877000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10716000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10848000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11030000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11201000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,31 +4816,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>32323000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>64640000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>32224000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>73801000</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>76513000</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>70461000</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>33342000</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4801,8 +4920,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>564881000</v>
+      </c>
+      <c r="E54" s="3">
         <v>556519000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>566162000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>561580000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>557334000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>558207000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>561777000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>557263000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>559477000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>540786000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>541246000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>557191000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>553515000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>554212000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>474414000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>466679000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>461817000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>458978000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>445493000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>410295000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>408916000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>405761000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>392837000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>382315000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,31 +5206,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>423966000</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>416391000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>425624000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>421418000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>423609000</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>427489000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>436833000</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5178,31 +5308,34 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2360000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3706000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>3922000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>3943000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>5225000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>4565000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3687000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5279,132 +5412,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15339000</v>
+        <v>200000</v>
       </c>
       <c r="E59" s="3">
-        <v>15785000</v>
+        <v>100000</v>
       </c>
       <c r="F59" s="3">
-        <v>15621000</v>
+        <v>200000</v>
       </c>
       <c r="G59" s="3">
-        <v>17437000</v>
+        <v>200000</v>
       </c>
       <c r="H59" s="3">
-        <v>15325000</v>
+        <v>200000</v>
       </c>
       <c r="I59" s="3">
-        <v>14376000</v>
+        <v>200000</v>
       </c>
       <c r="J59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="K59" s="3">
         <v>15762000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19245000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15622000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14623000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12741000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14199000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11186000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11931000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9514000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10629000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12345000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17150000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11831000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12220000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13804000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12793000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9002000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>437958000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>431730000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>439209000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>432946000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>438546000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>440414000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>448809000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5481,132 +5620,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>36391000</v>
+        <v>68069000</v>
       </c>
       <c r="E61" s="3">
-        <v>35707000</v>
+        <v>71391000</v>
       </c>
       <c r="F61" s="3">
-        <v>34737000</v>
+        <v>72707000</v>
       </c>
       <c r="G61" s="3">
-        <v>30167000</v>
+        <v>74330000</v>
       </c>
       <c r="H61" s="3">
-        <v>31384000</v>
+        <v>66167000</v>
       </c>
       <c r="I61" s="3">
-        <v>28802000</v>
+        <v>65384000</v>
       </c>
       <c r="J61" s="3">
+        <v>60822000</v>
+      </c>
+      <c r="K61" s="3">
         <v>26638000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24558000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25984000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26571000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30784000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>33471000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>34813000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31530000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33695000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>36610000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>38526000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>49908000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>43922000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>39453000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>39649000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>39468000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>35918000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>3125000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>717000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>2872000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>3163000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3140000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>3063000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>3072000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5683,8 +5828,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>503877000</v>
+        <v>509152000</v>
       </c>
       <c r="E66" s="3">
-        <v>514822000</v>
+        <v>503838000</v>
       </c>
       <c r="F66" s="3">
-        <v>510475000</v>
+        <v>514788000</v>
       </c>
       <c r="G66" s="3">
-        <v>507880000</v>
+        <v>510439000</v>
       </c>
       <c r="H66" s="3">
-        <v>508887000</v>
+        <v>507853000</v>
       </c>
       <c r="I66" s="3">
-        <v>512733000</v>
+        <v>508861000</v>
       </c>
       <c r="J66" s="3">
+        <v>512703000</v>
+      </c>
+      <c r="K66" s="3">
         <v>511489000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>512789000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>493134000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>492065000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>501496000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>497256000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>499585000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>420565000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>412669000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>408541000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>406055000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>396230000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>360981000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>359496000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>356421000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>344301000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>334587000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,31 +6490,34 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>6247000</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>6245000</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>6243000</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>6241000</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>7239000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>7237000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>7235000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58412000</v>
+      </c>
+      <c r="E72" s="3">
         <v>57652000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>56913000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56290000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>56170000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>55346000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>54598000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>53572000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52777000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51841000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>51058000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>50228000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>49541000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>48663000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>48113000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>46848000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>45947000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>44986000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41885000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>42215000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>41413000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>40616000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>39742000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>38919000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>52642000</v>
+        <v>49442000</v>
       </c>
       <c r="E76" s="3">
-        <v>51340000</v>
+        <v>46397000</v>
       </c>
       <c r="F76" s="3">
-        <v>51105000</v>
+        <v>45097000</v>
       </c>
       <c r="G76" s="3">
-        <v>49454000</v>
+        <v>44864000</v>
       </c>
       <c r="H76" s="3">
-        <v>49320000</v>
+        <v>42215000</v>
       </c>
       <c r="I76" s="3">
-        <v>49044000</v>
+        <v>42083000</v>
       </c>
       <c r="J76" s="3">
+        <v>41809000</v>
+      </c>
+      <c r="K76" s="3">
         <v>45774000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46688000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47652000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>49181000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>55695000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>56259000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>54627000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53849000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>54010000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>53276000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>52923000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49263000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>49314000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>49420000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>49340000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>48536000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>47728000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1490000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1459000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>864000</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1554000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1483000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1677000</v>
+      </c>
+      <c r="K81" s="3">
+        <v>1401000</v>
+      </c>
+      <c r="L81" s="3">
+        <v>1550000</v>
+      </c>
+      <c r="M81" s="3">
+        <v>1402000</v>
+      </c>
+      <c r="N81" s="3">
         <v>1355000</v>
       </c>
-      <c r="E81" s="3">
-        <v>1240000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>740000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1440000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1347000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1599000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1401000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1550000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1402000</v>
-      </c>
-      <c r="M81" s="3">
-        <v>1355000</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1214000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1408000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1750000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1387000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1447000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3592000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>840000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1299000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1304000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1298000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1188000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1276000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>967000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>975000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>37000</v>
+        <v>49000</v>
       </c>
       <c r="E83" s="3">
-        <v>37000</v>
+        <v>60000</v>
       </c>
       <c r="F83" s="3">
-        <v>43000</v>
+        <v>65000</v>
       </c>
       <c r="G83" s="3">
-        <v>49000</v>
+        <v>64000</v>
       </c>
       <c r="H83" s="3">
-        <v>60000</v>
+        <v>58000</v>
       </c>
       <c r="I83" s="3">
-        <v>65000</v>
+        <v>144000</v>
       </c>
       <c r="J83" s="3">
+        <v>385000</v>
+      </c>
+      <c r="K83" s="3">
         <v>64000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>58000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>144000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>385000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>558000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>421000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>419000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>375000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>553000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>232000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>384000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>328000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>411000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>325000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>307000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>272000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>290000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>272000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>287000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>280000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>258000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>291000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>289000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>279000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>276000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3287000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1035000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1758000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4864000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>115000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3256000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1876000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4046000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3394000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2632000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-989000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3494000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1525000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1415000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>780000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1935000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>393000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3027000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-696000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3115000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>604000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2243000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1401000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>873000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>675000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,31 +8341,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8223,8 +8443,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3782000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-220000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6365000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4665000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-9251000</v>
-      </c>
       <c r="H94" s="3">
+        <v>4913000</v>
+      </c>
+      <c r="I94" s="3">
         <v>13249000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12707000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3312000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9022000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>805000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>851000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>162000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-623000</v>
+        <v>646000</v>
       </c>
       <c r="E96" s="3">
-        <v>-624000</v>
+        <v>623000</v>
       </c>
       <c r="F96" s="3">
-        <v>-624000</v>
+        <v>624000</v>
       </c>
       <c r="G96" s="3">
-        <v>-624000</v>
+        <v>624000</v>
       </c>
       <c r="H96" s="3">
-        <v>-606000</v>
+        <v>624000</v>
       </c>
       <c r="I96" s="3">
-        <v>-607000</v>
+        <v>606000</v>
       </c>
       <c r="J96" s="3">
+        <v>607000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-612000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-622000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-626000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-531000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-533000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-538000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-492000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-493000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-492000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-494000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-491000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-503000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-509000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-518000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-432000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-436000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-442000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,132 +9209,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11271000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3619000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1422000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2733000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-796000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16262000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>68000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4724000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5730000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5196000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3040000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13676000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>26507000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>540000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2893000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9571000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4076000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>538000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>368000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9169,105 +9417,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1905000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10456000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-988000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1621000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-11830000</v>
-      </c>
       <c r="H102" s="3">
+        <v>2334000</v>
+      </c>
+      <c r="I102" s="3">
         <v>11190000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>495000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1010000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-432000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-839000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>119000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1269000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>438000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>388000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>291000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2432000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-610000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>255000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>354000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-546000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>360000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>776000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>513000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>36000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>124000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>348000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,235 +656,241 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5411000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5189000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5176000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4990000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5129000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5104000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5147000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5368000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5109000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4132000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3281000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2975000</v>
       </c>
       <c r="P8" s="3">
         <v>2975000</v>
       </c>
       <c r="Q8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="R8" s="3">
         <v>2701000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2483000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2576000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2676000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2855000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3200000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3334000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3503000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3497000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3428000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3348000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -987,35 +993,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5411000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5189000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5176000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4990000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5129000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5104000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5147000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5368000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1091,8 +1100,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,8 +1353,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1363,8 +1382,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1441,35 +1460,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E15" s="3">
         <v>21000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>37000</v>
       </c>
       <c r="F15" s="3">
         <v>37000</v>
       </c>
       <c r="G15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="H15" s="3">
         <v>43000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>49000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>60000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>65000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1545,8 +1567,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3506000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3327000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3357000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3334000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4074000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3245000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3372000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3321000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1833000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>898000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>266000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-98000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-214000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>422000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-416000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>152000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>192000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>328000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>689000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1067000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1182000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1179000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1142000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>970000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>815000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>724000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>649000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>612000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>586000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>522000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>457000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>384000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1905000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1862000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1819000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1656000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1055000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1859000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1775000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2047000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3276000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3234000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3015000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3012000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3189000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3059000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2279000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2899000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2424000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2484000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2527000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2511000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2267000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2321000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2318000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2286000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2378000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,8 +1858,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1852,190 +1885,196 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-964000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-702000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-670000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-786000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-929000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-885000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-894000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-992000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-763000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2069000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1883000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1856000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1693000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1098000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1908000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1835000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2112000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1945000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2086000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1980000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2113000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2221000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2234000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1734000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2572000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2307000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1930000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-518000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1207000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1749000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1761000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1731000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1566000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1905000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,8 +2099,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2138,216 +2177,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1905000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1862000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1819000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1656000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1055000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1859000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1775000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2047000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1881000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2028000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1836000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1728000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1663000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1813000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1315000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2197000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1754000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1698000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-902000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>879000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1338000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1436000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1424000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1294000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1615000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E24" s="3">
         <v>357000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>342000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>312000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>172000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>289000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>275000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>353000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>333000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>388000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>340000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>299000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>357000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>323000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>212000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>371000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>298000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>166000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-158000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>120000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>195000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>255000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>239000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>212000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>264000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>261000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>304000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>253000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>183000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>413000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>386000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>320000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>319000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1505000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1477000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1344000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>883000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1570000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1694000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1548000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1640000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1496000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1429000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1306000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1490000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1103000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1826000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1456000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1532000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-744000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>759000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1143000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1181000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1185000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1082000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1351000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>891000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1505000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1396000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1355000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1240000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>740000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1440000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1347000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1599000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1401000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1550000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1402000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1355000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1214000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1408000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1037000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1750000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1387000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1447000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-807000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>684000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1061000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1093000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1109000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>999000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1276000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>815000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>967000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>975000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2800,8 +2860,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
@@ -2812,32 +2872,32 @@
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>4399000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>156000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>238000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>211000</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>189000</v>
       </c>
       <c r="Z29" s="3">
         <v>189000</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>189000</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2848,12 +2908,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,8 +3140,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3100,190 +3169,196 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>1395000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1206000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1179000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1284000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1526000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1246000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>964000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>702000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>670000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>786000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3429000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1632000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>929000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>885000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>894000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>992000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>763000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>746000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>701000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>775000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>669000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>670000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>668000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>705000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1490000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1459000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1330000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>864000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1554000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1483000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1677000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1401000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1550000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1402000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1355000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1214000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1408000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1037000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1750000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1387000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1447000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3592000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>840000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1299000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1298000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1188000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1276000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>967000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>975000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1490000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1459000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1330000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>864000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1554000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1483000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1677000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1401000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1550000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1402000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1355000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1214000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1408000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1037000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1750000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1387000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1447000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3592000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>840000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1299000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1298000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1188000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1276000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>967000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>975000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,216 +3760,223 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5936000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5702000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5368000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4999000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5936000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4782000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5604000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5335000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7043000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6548000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8582000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7572000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8004000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8843000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8724000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7455000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7017000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6629000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6338000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7493000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5061000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5671000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5416000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5062000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5608000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3937000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4083000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3449000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>56821000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4200000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3699000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3811000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37191000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27320000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>40278000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>28404000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>48776000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>74250000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>75478000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>72447000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>86161000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>85173000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>70959000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>50233000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>19986000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>23413000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>19036000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>18362000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>15261000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>10893000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3909,8 +4001,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3987,8 +4079,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3996,26 +4091,26 @@
         <v>31000</v>
       </c>
       <c r="E44" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F44" s="3">
         <v>34000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>35000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>36000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>35000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>36000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>38000</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -4091,35 +4186,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1870000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1881000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2020000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1884000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1925000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1789000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1731000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1692000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4195,35 +4293,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13592000</v>
+      </c>
+      <c r="E46" s="3">
         <v>47931000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12733000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>65416000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13816000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11746000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12604000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>45859000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4299,117 +4400,123 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>149332000</v>
+      </c>
+      <c r="E47" s="3">
         <v>153400000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>147682000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>138740000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>140883000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>140433000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>143676000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>146562000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8437000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8130000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8441000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7798000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8180000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7737000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7521000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6386000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6052000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4938000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4943000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13205000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13734000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13325000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13001000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12567000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12894000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>1619000</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
@@ -4417,20 +4524,20 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3">
         <v>1745000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4450,23 +4557,23 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>1876000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W48" s="3">
-        <v>2000000</v>
+      <c r="W48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X48" s="3">
         <v>2000000</v>
@@ -4475,11 +4582,11 @@
         <v>2000000</v>
       </c>
       <c r="Z48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="AA48" s="3">
         <v>2144000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4489,8 +4596,8 @@
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF48" s="3">
         <v>0</v>
@@ -4507,112 +4614,118 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14643000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14435000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14671000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14694000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14618000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14993000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14442000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14280000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14410000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14193000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13524000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13124000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12734000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12718000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12751000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10997000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10475000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10346000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10300000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10315000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10877000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10716000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10848000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11201000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,35 +4935,38 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>68871000</v>
+      </c>
+      <c r="E52" s="3">
         <v>32323000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>64640000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32224000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>73801000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>76513000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>70461000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33342000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4923,8 +5042,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>560038000</v>
+      </c>
+      <c r="E54" s="3">
         <v>564881000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>556519000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>566162000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>561580000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>557334000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>558207000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>561777000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>557263000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>559477000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>540786000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>541246000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>557191000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>553515000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>554212000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>474414000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>466679000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>461817000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>458978000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>445493000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>410295000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>408916000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>405761000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>392837000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>382315000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,35 +5336,36 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>426738000</v>
+      </c>
+      <c r="E57" s="3">
         <v>423966000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>416391000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>425624000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>421418000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>423609000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>427489000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>436833000</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -5311,35 +5441,38 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3569000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2360000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3706000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3922000</v>
       </c>
-      <c r="G58" s="3">
-        <v>3943000</v>
-      </c>
       <c r="H58" s="3">
+        <v>3538000</v>
+      </c>
+      <c r="I58" s="3">
         <v>5225000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4565000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3687000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5415,8 +5548,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5424,16 +5560,16 @@
         <v>200000</v>
       </c>
       <c r="E59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="F59" s="3">
         <v>100000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>200000</v>
       </c>
       <c r="G59" s="3">
         <v>200000</v>
       </c>
-      <c r="H59" s="3">
-        <v>200000</v>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I59" s="3">
         <v>200000</v>
@@ -5442,112 +5578,115 @@
         <v>200000</v>
       </c>
       <c r="K59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="L59" s="3">
         <v>15762000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19245000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15622000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14623000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12741000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14199000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11186000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11931000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9514000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10629000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12345000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17150000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11831000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12220000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13804000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12793000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9002000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>438808000</v>
+      </c>
+      <c r="E60" s="3">
         <v>437958000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>431730000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>439209000</v>
       </c>
-      <c r="G60" s="3">
-        <v>432946000</v>
-      </c>
       <c r="H60" s="3">
+        <v>432541000</v>
+      </c>
+      <c r="I60" s="3">
         <v>438546000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>440414000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>448809000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5623,139 +5762,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>63142000</v>
+      </c>
+      <c r="E61" s="3">
         <v>68069000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>71391000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>72707000</v>
       </c>
-      <c r="G61" s="3">
-        <v>74330000</v>
-      </c>
       <c r="H61" s="3">
+        <v>74735000</v>
+      </c>
+      <c r="I61" s="3">
         <v>66167000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>65384000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>60822000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26638000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24558000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25984000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26571000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30784000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33471000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>34813000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31530000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>33695000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>36610000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>38526000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>49908000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>43922000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>39453000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>39649000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>39468000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>35918000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3619000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3125000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>717000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2872000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3163000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3140000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3063000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3072000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5831,8 +5976,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>505569000</v>
+      </c>
+      <c r="E66" s="3">
         <v>509152000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>503838000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>514788000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>510439000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>507853000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>508861000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>512703000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>511489000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>512789000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>493134000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>492065000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>501496000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>497256000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>499585000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>420565000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>412669000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>408541000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>406055000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>396230000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>360981000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>359496000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>356421000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>344301000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>334587000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,35 +6657,38 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>5749000</v>
+      </c>
+      <c r="E70" s="3">
         <v>6247000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>6245000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>6243000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>6241000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>7239000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>7237000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>7235000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>59282000</v>
+      </c>
+      <c r="E72" s="3">
         <v>58412000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>57652000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56913000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>56290000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56170000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>55346000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>54598000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>53572000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>52777000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>51841000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51058000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50228000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>49541000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>48663000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>48113000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>46848000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>45947000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>44986000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>41885000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>42215000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>41413000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>40616000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39742000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>38919000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48676000</v>
+      </c>
+      <c r="E76" s="3">
         <v>49442000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>46397000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45097000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44864000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>42215000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>42083000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>41809000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45774000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46688000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47652000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>49181000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55695000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56259000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>54627000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>53849000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>54010000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>53276000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>52923000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>49263000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>49314000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>49420000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>49340000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>48536000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>47728000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1490000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1459000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1330000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>864000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1554000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1483000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1677000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1401000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1550000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1402000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1355000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1214000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1408000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1037000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1750000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1387000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1447000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3592000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>840000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1299000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1298000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1188000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1276000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>967000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>975000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,112 +7773,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E83" s="3">
         <v>49000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>60000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>65000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>58000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>144000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>385000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>64000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>58000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>144000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>385000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>558000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>421000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>419000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>375000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>553000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>232000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>384000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>328000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>411000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>325000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>307000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>272000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>290000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>272000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>287000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>280000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>258000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>291000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>289000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>279000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>276000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3287000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1035000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1758000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4864000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>115000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3256000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1876000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4046000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3394000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2632000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-989000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3494000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1525000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1415000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>780000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1935000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>393000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3027000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-696000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3115000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>604000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2243000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1401000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2137000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>873000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>675000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,8 +8561,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8368,8 +8588,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8446,8 +8666,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7135000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3782000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-220000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6365000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-4665000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-2345000</v>
+      </c>
+      <c r="I94" s="3">
         <v>4913000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>13249000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>12707000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3312000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>9022000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>805000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>851000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>162000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,19 +9028,20 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E96" s="3">
         <v>646000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>623000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>624000</v>
       </c>
       <c r="G96" s="3">
         <v>624000</v>
@@ -8817,91 +9050,94 @@
         <v>624000</v>
       </c>
       <c r="I96" s="3">
+        <v>624000</v>
+      </c>
+      <c r="J96" s="3">
         <v>606000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>607000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-612000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-622000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-626000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-531000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-533000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-538000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-492000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-493000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-492000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-494000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-491000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-503000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-509000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-518000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-432000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-436000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-442000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,112 +9454,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3870000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2400000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11271000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3619000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1422000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2733000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-796000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16262000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>68000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4724000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5730000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5196000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3040000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>13676000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>26507000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>540000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2893000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>9571000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4076000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>538000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>368000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9342,8 +9590,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9420,108 +9668,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5065000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1905000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10456000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-988000</v>
       </c>
-      <c r="G102" s="3">
-        <v>1621000</v>
-      </c>
       <c r="H102" s="3">
+        <v>3941000</v>
+      </c>
+      <c r="I102" s="3">
         <v>2334000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11190000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>495000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1010000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-432000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-839000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>119000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1269000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>438000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>388000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>291000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2432000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-610000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>255000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>354000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-546000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>360000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>776000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>513000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>36000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>124000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>348000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,241 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5233000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5411000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5189000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5176000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4990000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5129000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5104000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5147000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5368000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5109000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4132000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3281000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2975000</v>
       </c>
       <c r="Q8" s="3">
         <v>2975000</v>
       </c>
       <c r="R8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="S8" s="3">
         <v>2701000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2483000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2576000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2676000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2855000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3200000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3334000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3503000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3497000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3428000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3348000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -996,38 +1002,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5233000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5411000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5189000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5176000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4990000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5129000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5104000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5147000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5368000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,8 +1372,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1385,8 +1404,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1463,38 +1482,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E15" s="3">
         <v>164000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>37000</v>
       </c>
       <c r="G15" s="3">
         <v>37000</v>
       </c>
       <c r="H15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I15" s="3">
         <v>43000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>49000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>60000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>65000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1592,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3387000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3506000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3327000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3357000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3334000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4074000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3245000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3372000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3321000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1833000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>898000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>266000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-98000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-214000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-84000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>422000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-416000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>152000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>192000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>328000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>689000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1067000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1182000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1179000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1142000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>970000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>815000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>724000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>649000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>612000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>586000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>522000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>457000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>384000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1846000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1905000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1862000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1819000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1656000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1055000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1859000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1775000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2047000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3276000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3234000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3015000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3012000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3189000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3059000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2279000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2899000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2424000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2484000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2527000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2511000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2267000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2321000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2318000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2286000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2378000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,8 +1891,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1888,193 +1921,199 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-964000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-702000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-670000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-786000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-929000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-885000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-894000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-992000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-763000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1936000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2069000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1883000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1856000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1693000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1098000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1908000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1835000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2112000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1945000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2086000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1980000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2113000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2221000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2234000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1734000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2572000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2307000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1930000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-518000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1207000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1749000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1761000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1731000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1566000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1905000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2102,8 +2141,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2180,222 +2219,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1846000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1905000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1862000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1819000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1656000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1055000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1859000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1775000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2047000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1881000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2028000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1836000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1728000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1663000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1813000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1315000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2197000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1754000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1698000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-902000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>879000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1338000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1436000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1424000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1294000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1615000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E24" s="3">
         <v>278000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>357000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>342000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>312000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>172000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>289000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>275000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>353000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>333000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>388000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>340000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>299000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>357000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>323000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>212000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>371000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>298000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>166000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-158000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>120000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>195000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>255000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>239000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>212000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>264000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>261000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>304000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>253000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>183000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>413000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>386000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>320000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>319000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1499000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1627000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1505000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1477000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1344000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>883000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1570000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1500000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1694000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1548000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1640000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1496000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1429000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1306000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1490000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1103000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1826000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1456000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1532000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-744000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>759000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1143000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1181000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1185000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1082000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1351000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>891000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1399000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1505000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1396000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1355000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1240000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>740000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1440000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1347000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1599000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1401000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1550000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1402000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1355000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1214000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1408000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1037000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1750000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1387000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1447000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-807000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>684000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1061000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1093000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1109000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>999000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1276000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>815000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>967000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>975000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2863,8 +2923,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>5</v>
@@ -2875,32 +2935,32 @@
       <c r="S29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>4399000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>156000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>238000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>211000</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>189000</v>
       </c>
       <c r="AA29" s="3">
         <v>189000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AB29" s="3">
+        <v>189000</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -2911,12 +2971,12 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,8 +3209,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3172,193 +3241,199 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>1395000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1206000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1179000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1284000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1526000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1246000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>964000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>702000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>670000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>786000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3429000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1632000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>929000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>885000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>894000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>992000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>763000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>746000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>701000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>775000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>669000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>670000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>668000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>705000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1481000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1610000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1490000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1459000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1330000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>864000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1554000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1483000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1677000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1401000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1550000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1402000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1355000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1214000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1408000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1037000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1750000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1387000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1447000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3592000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>840000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1299000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1304000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1298000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1276000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>967000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>975000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1481000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1610000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1490000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1459000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1330000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>864000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1554000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1483000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1677000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1401000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1550000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1402000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1355000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1214000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1408000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1037000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1750000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1387000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1447000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3592000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>840000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1299000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1304000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1298000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1276000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>967000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>975000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,222 +3846,229 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5110000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5936000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5702000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5368000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4999000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5936000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4782000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5604000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5335000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7043000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6548000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8582000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7572000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8004000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8843000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8724000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7455000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7017000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6629000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6338000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7493000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5061000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5671000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5416000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5062000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5608000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5783000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3937000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4083000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3449000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>56821000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4200000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3699000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3811000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37191000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27320000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>40278000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>28404000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>48776000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>74250000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>75478000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>72447000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>86161000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>85173000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>70959000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>50233000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>19986000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>23413000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>19036000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>18362000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>15261000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>10893000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4004,8 +4096,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4082,38 +4174,41 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="E44" s="3">
         <v>31000</v>
       </c>
       <c r="F44" s="3">
+        <v>31000</v>
+      </c>
+      <c r="G44" s="3">
         <v>34000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>36000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>35000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>36000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>38000</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -4189,38 +4284,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1763000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1870000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1881000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2020000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1884000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1925000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1789000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1731000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1692000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4296,38 +4394,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46816000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13592000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>47931000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12733000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>65416000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13816000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11746000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12604000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>45859000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4403,144 +4504,150 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>147223000</v>
+      </c>
+      <c r="E47" s="3">
         <v>149332000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>153400000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>147682000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>138740000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>140883000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>140433000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>143676000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>146562000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8437000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8130000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8441000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7798000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8180000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7737000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7521000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6386000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6052000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4938000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4943000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13205000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13734000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13325000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13001000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12567000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12894000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
         <v>1619000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>1745000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4560,23 +4667,23 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>1876000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X48" s="3">
-        <v>2000000</v>
+      <c r="X48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y48" s="3">
         <v>2000000</v>
@@ -4585,11 +4692,11 @@
         <v>2000000</v>
       </c>
       <c r="AA48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="AB48" s="3">
         <v>2144000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4599,8 +4706,8 @@
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF48" s="3">
-        <v>0</v>
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
@@ -4617,115 +4724,121 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14496000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14643000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14435000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14671000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14694000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14618000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14993000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14442000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14280000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14410000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14193000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13524000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13124000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12734000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12718000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>12751000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10997000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10475000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10346000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10300000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10315000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10877000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10716000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10848000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11201000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,38 +5054,41 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>31881000</v>
+      </c>
+      <c r="E52" s="3">
         <v>68871000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>32323000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>64640000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>32224000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>73801000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>76513000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>70461000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>33342000</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -5045,8 +5164,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>554722000</v>
+      </c>
+      <c r="E54" s="3">
         <v>560038000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>564881000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>556519000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>566162000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>561580000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>557334000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>558207000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>561777000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>557263000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>559477000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>540786000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>541246000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>557191000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>553515000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>554212000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>474414000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>466679000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>461817000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>458978000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>445493000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>410295000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>408916000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>405761000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>392837000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>382315000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,38 +5466,39 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>422915000</v>
+      </c>
+      <c r="E57" s="3">
         <v>426738000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>423966000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>416391000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>425624000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>421418000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>423609000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>427489000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>436833000</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -5444,38 +5574,41 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3569000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2360000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3706000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3922000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3538000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5225000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4565000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3687000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5551,8 +5684,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5563,16 +5699,16 @@
         <v>200000</v>
       </c>
       <c r="F59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="G59" s="3">
         <v>100000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>200000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" s="3">
-        <v>200000</v>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J59" s="3">
         <v>200000</v>
@@ -5581,115 +5717,118 @@
         <v>200000</v>
       </c>
       <c r="L59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="M59" s="3">
         <v>15762000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19245000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15622000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14623000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12741000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14199000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11186000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11931000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9514000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10629000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12345000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17150000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11831000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12220000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13804000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12793000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9002000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>433975000</v>
+      </c>
+      <c r="E60" s="3">
         <v>438808000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>437958000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>431730000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>439209000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>432541000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>438546000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>440414000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>448809000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5765,145 +5904,151 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>60722000</v>
+      </c>
+      <c r="E61" s="3">
         <v>63142000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>68069000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>71391000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>72707000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>74735000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>66167000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>65384000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>60822000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26638000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24558000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25984000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26571000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>30784000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>33471000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>34813000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31530000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33695000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>36610000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>38526000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>49908000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>43922000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>39453000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>39649000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>39468000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35918000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3574000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3619000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3125000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>717000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2872000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3163000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3140000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3063000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3072000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5979,8 +6124,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>498271000</v>
+      </c>
+      <c r="E66" s="3">
         <v>505569000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>509152000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>503838000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>514788000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>510439000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>507853000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>508861000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>512703000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>511489000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>512789000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>493134000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>492065000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>501496000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>497256000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>499585000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>420565000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>412669000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>408541000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>406055000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>396230000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>360981000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>359496000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>356421000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>344301000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>334587000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,38 +6824,41 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>5751000</v>
+      </c>
+      <c r="E70" s="3">
         <v>5749000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>6247000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>6245000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>6243000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>6241000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>7239000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>7237000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>7235000</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60051000</v>
+      </c>
+      <c r="E72" s="3">
         <v>59282000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58412000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>57652000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>56913000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56290000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56170000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>55346000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>54598000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53572000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52777000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51841000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>51058000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50228000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>49541000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>48663000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>48113000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>46848000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>45947000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>44986000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>41885000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>42215000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>41413000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>40616000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39742000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>38919000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50654000</v>
+      </c>
+      <c r="E76" s="3">
         <v>48676000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49442000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46397000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45097000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44864000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>42215000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42083000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41809000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45774000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46688000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47652000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>49181000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>55695000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56259000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>54627000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>53849000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>54010000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>53276000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>52923000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>49263000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>49314000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>49420000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>49340000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>48536000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>47728000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1481000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1610000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1490000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1459000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1330000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>864000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1554000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1483000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1677000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1401000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1550000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1402000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1355000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1214000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1408000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1037000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1750000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1387000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1447000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3592000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>840000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1299000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1304000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1298000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1276000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>967000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>975000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E83" s="3">
         <v>43000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>65000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>64000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>58000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>144000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>385000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>64000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>58000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>144000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>385000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>558000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>421000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>419000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>375000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>553000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>232000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>384000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>328000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>411000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>325000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>307000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>272000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>290000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>272000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>287000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>280000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>258000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>291000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>289000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>279000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>276000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-509000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1800000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3287000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1035000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1758000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4864000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>115000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3256000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1876000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4046000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3394000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2632000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-989000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3494000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1525000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1415000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>780000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1935000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>393000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3027000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-696000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3115000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>604000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2243000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1401000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2137000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>873000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>675000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,8 +8781,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8591,8 +8811,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8669,8 +8889,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-980000</v>
+      </c>
+      <c r="E94" s="3">
         <v>7135000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3782000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-220000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-6365000</v>
-      </c>
       <c r="H94" s="3">
+        <v>3443000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2345000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4913000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>13249000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>12707000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3312000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>9022000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>805000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>851000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>162000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,22 +9261,23 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>639000</v>
+      </c>
+      <c r="E96" s="3">
         <v>644000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>646000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>623000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>624000</v>
       </c>
       <c r="H96" s="3">
         <v>624000</v>
@@ -9053,91 +9286,94 @@
         <v>624000</v>
       </c>
       <c r="J96" s="3">
+        <v>624000</v>
+      </c>
+      <c r="K96" s="3">
         <v>606000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>607000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-612000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-622000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-626000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-531000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-533000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-538000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-492000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-493000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-492000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-494000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-491000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-503000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-509000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-518000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-432000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-436000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-442000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,115 +9699,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6362000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3870000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2400000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11271000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3619000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1422000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2733000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-796000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>16262000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>68000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4724000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5730000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5196000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3040000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>13676000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>26507000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>540000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2893000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9571000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4076000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>538000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>368000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9593,8 +9841,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9671,111 +9919,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7851000</v>
+      </c>
+      <c r="E102" s="3">
         <v>5065000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1905000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10456000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-988000</v>
-      </c>
       <c r="H102" s="3">
+        <v>8820000</v>
+      </c>
+      <c r="I102" s="3">
         <v>3941000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2334000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>11190000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>495000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1010000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-432000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-839000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>119000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1269000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>438000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>388000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>291000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2432000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>255000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>354000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-546000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>360000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>776000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>513000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>36000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>124000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>348000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,247 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5407000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5233000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5411000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5189000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5176000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4990000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5129000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5104000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5147000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5368000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5109000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4132000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3281000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>2975000</v>
       </c>
       <c r="R8" s="3">
         <v>2975000</v>
       </c>
       <c r="S8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="T8" s="3">
         <v>2701000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2483000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2576000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2676000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2855000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3200000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3334000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3503000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3497000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3428000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3348000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1005,41 +1011,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5407000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5233000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5411000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5189000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5176000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4990000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5129000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5104000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5147000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5368000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1265,8 +1278,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,8 +1391,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1407,8 +1426,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1485,41 +1504,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E15" s="3">
         <v>90000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>164000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>37000</v>
       </c>
       <c r="H15" s="3">
         <v>37000</v>
       </c>
       <c r="I15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J15" s="3">
         <v>43000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>60000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>65000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3383000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3387000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3506000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3327000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3357000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3334000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4074000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3245000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3372000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3321000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1833000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>898000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>266000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-98000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-214000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-84000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>422000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-416000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>152000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>192000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>328000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>689000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1067000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1182000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1179000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1142000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>970000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>815000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>724000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>649000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>612000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>586000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>522000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>457000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>384000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2024000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1846000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1905000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1862000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1819000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1656000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1055000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1859000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1775000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2047000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3276000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3234000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3015000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3012000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3189000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3059000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2279000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2899000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2424000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2484000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2527000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2511000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2267000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2321000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2318000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2286000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2378000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,8 +1924,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1924,196 +1957,202 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-964000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-702000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-670000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-786000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-929000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-885000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-894000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-992000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-763000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1936000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2069000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1883000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1856000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1693000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1098000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1908000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1835000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2112000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1945000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2086000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1980000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2113000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2221000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2234000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1734000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2572000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2307000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1930000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-518000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1207000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1749000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1761000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1731000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1566000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1905000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2144,8 +2183,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2222,228 +2261,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2024000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1846000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1905000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1862000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1819000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1656000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1055000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1859000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1775000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2047000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1881000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2028000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1836000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1728000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1663000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1813000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1315000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2197000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1754000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1698000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-902000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>879000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1338000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1436000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1424000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1294000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1615000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>381000</v>
+      </c>
+      <c r="E24" s="3">
         <v>347000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>278000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>357000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>342000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>312000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>172000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>289000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>275000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>353000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>333000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>388000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>340000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>299000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>357000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>323000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>212000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>371000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>298000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>166000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-158000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>120000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>195000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>255000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>239000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>212000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>264000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>261000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>304000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>253000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>183000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>413000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>386000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>320000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>319000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1499000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1627000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1505000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1477000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1344000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>883000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1570000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1500000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1694000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1548000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1640000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1496000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1429000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1306000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1490000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1103000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1826000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1456000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1532000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-744000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>759000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1143000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1181000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1185000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1082000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1351000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>891000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1532000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1399000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1505000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1396000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1355000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1240000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>740000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1440000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1347000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1599000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1401000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1550000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1402000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1214000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1408000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1037000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1750000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1387000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1447000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-807000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>684000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1061000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1093000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1109000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>999000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>815000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>967000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>975000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2926,8 +2986,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -2938,32 +2998,32 @@
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>4399000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>156000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>238000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>211000</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>189000</v>
       </c>
       <c r="AB29" s="3">
         <v>189000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>189000</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -2974,12 +3034,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2992,8 +3052,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,8 +3278,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3244,196 +3313,202 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>1395000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1206000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1179000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1284000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1526000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1246000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>964000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>702000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>670000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>786000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3429000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1632000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>929000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>885000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>894000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>992000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>763000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>746000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>701000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>775000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>669000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>670000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>668000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>705000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1481000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1610000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1490000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1459000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1330000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>864000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1554000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1483000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1677000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1401000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1550000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1402000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1214000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1408000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1037000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1750000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1387000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1447000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3592000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>840000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1299000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1304000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1298000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>967000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>975000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1481000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1610000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1490000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1459000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1330000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>864000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1554000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1483000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1677000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1401000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1550000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1402000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1214000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1408000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1037000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1750000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1387000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1447000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3592000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>840000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1299000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1304000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1298000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>967000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>975000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,228 +3932,235 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4947000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5110000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5936000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5702000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5368000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4999000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5936000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4782000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5604000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5335000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7043000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6548000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8582000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7572000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8004000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8843000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8724000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7455000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7017000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6629000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6338000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7493000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5061000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5671000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5416000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5062000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5608000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6129000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5783000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3937000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4083000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3449000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>56821000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4200000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3699000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3811000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>37191000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27320000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>40278000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>28404000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>48776000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>74250000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>75478000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>72447000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>86161000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>85173000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>70959000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>50233000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>19986000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>23413000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19036000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>18362000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>15261000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10893000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4099,8 +4191,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4177,41 +4269,44 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E44" s="3">
         <v>32000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>31000</v>
       </c>
       <c r="F44" s="3">
         <v>31000</v>
       </c>
       <c r="G44" s="3">
+        <v>31000</v>
+      </c>
+      <c r="H44" s="3">
         <v>34000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>35000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>36000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>36000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>38000</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -4287,41 +4382,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1860000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1763000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1870000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1881000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2020000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1884000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1925000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1789000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1731000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1692000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4397,41 +4495,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>46816000</v>
+        <v>15798000</v>
       </c>
       <c r="E46" s="3">
+        <v>14916000</v>
+      </c>
+      <c r="F46" s="3">
         <v>13592000</v>
       </c>
-      <c r="F46" s="3">
-        <v>47931000</v>
-      </c>
       <c r="G46" s="3">
+        <v>13331000</v>
+      </c>
+      <c r="H46" s="3">
         <v>12733000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>65416000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13816000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11746000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12604000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45859000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4507,150 +4608,156 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>152103000</v>
+      </c>
+      <c r="E47" s="3">
         <v>147223000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>149332000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>153400000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>147682000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>138740000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>140883000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>140433000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>143676000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>146562000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8437000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8130000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8441000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7798000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8180000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7737000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7521000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6386000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6052000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4938000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4943000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13205000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13734000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13325000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13001000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12567000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12894000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>1619000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>1745000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4670,23 +4777,23 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>1876000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y48" s="3">
-        <v>2000000</v>
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z48" s="3">
         <v>2000000</v>
@@ -4695,11 +4802,11 @@
         <v>2000000</v>
       </c>
       <c r="AB48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="AC48" s="3">
         <v>2144000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4709,8 +4816,8 @@
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG48" s="3">
-        <v>0</v>
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
@@ -4727,118 +4834,124 @@
       <c r="AL48" s="3">
         <v>0</v>
       </c>
+      <c r="AM48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14399000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14496000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14643000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14435000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14671000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14694000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14618000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14993000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14442000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14280000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14410000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14193000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13524000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13124000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12734000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>12718000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>12751000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10997000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10475000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10346000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10300000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10315000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10877000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10716000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10848000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11201000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,41 +5173,44 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>31881000</v>
+        <v>54990000</v>
       </c>
       <c r="E52" s="3">
+        <v>63781000</v>
+      </c>
+      <c r="F52" s="3">
         <v>68871000</v>
       </c>
-      <c r="F52" s="3">
-        <v>32323000</v>
-      </c>
       <c r="G52" s="3">
+        <v>66923000</v>
+      </c>
+      <c r="H52" s="3">
         <v>64640000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32224000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>73801000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>76513000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>70461000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>33342000</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -5167,8 +5286,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>559107000</v>
+      </c>
+      <c r="E54" s="3">
         <v>554722000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>560038000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>564881000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>556519000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>566162000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>561580000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>557334000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>558207000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>561777000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>557263000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>559477000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>540786000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>541246000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>557191000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>553515000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>554212000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>474414000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>466679000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>461817000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>458978000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>445493000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>410295000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>408916000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>405761000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>392837000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>382315000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,41 +5596,42 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>426696000</v>
+      </c>
+      <c r="E57" s="3">
         <v>422915000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>426738000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>423966000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>416391000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>425624000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>421418000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>423609000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>427489000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>436833000</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -5577,41 +5707,44 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2053000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2375000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3569000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2360000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3706000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3922000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3538000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5225000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4565000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3687000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5687,8 +5820,11 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5702,16 +5838,16 @@
         <v>200000</v>
       </c>
       <c r="G59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="H59" s="3">
         <v>100000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>200000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200000</v>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>200000</v>
@@ -5720,118 +5856,121 @@
         <v>200000</v>
       </c>
       <c r="M59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="N59" s="3">
         <v>15762000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19245000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15622000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14623000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12741000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14199000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11186000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11931000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9514000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10629000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12345000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17150000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11831000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12220000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13804000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12793000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9002000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>437269000</v>
+      </c>
+      <c r="E60" s="3">
         <v>433975000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>438808000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>437958000</v>
       </c>
-      <c r="G60" s="3">
-        <v>431730000</v>
-      </c>
       <c r="H60" s="3">
+        <v>429330000</v>
+      </c>
+      <c r="I60" s="3">
         <v>439209000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>432541000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>438546000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>440414000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>448809000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5907,151 +6046,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>60424000</v>
+      </c>
+      <c r="E61" s="3">
         <v>60722000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>63142000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>68069000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>71391000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>72707000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>74735000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>66167000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>65384000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>60822000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26638000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24558000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25984000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26571000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30784000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33471000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>34813000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31530000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33695000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>36610000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>38526000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>49908000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>43922000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>39453000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>39649000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>39468000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35918000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3759000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3574000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3619000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3125000</v>
       </c>
-      <c r="G62" s="3">
-        <v>717000</v>
-      </c>
       <c r="H62" s="3">
+        <v>3117000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2872000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3163000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3140000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3063000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3072000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6127,8 +6272,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>501452000</v>
+      </c>
+      <c r="E66" s="3">
         <v>498271000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>505569000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>509152000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>503838000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>514788000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>510439000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>507853000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>508861000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>512703000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>511489000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>512789000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>493134000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>492065000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>501496000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>497256000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>499585000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>420565000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>412669000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>408541000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>406055000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>396230000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>360981000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>359496000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>356421000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>344301000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>334587000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,41 +6991,44 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>5753000</v>
+      </c>
+      <c r="E70" s="3">
         <v>5751000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>5749000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>6247000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>6245000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>6243000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>6241000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>7239000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>7237000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>7235000</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -6937,8 +7104,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60951000</v>
+      </c>
+      <c r="E72" s="3">
         <v>60051000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59282000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58412000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>57652000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56913000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56290000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56170000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>55346000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>54598000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53572000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52777000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>51841000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>51058000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50228000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>49541000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>48663000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>48113000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>46848000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>45947000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>44986000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>41885000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>42215000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>41413000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>40616000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>39742000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>38919000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51854000</v>
+      </c>
+      <c r="E76" s="3">
         <v>50654000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>48676000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49442000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46397000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45097000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44864000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42215000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>42083000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>41809000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45774000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46688000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47652000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49181000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>55695000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>56259000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>54627000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>53849000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>54010000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53276000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>52923000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>49263000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>49314000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>49420000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>49340000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>48536000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>47728000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1481000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1610000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1490000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1459000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1330000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>864000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1554000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1483000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1677000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1401000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1550000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1402000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1214000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1408000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1037000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1750000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1387000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1447000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3592000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>840000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1299000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1304000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1298000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>967000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>975000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,8 +8169,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7981,109 +8179,112 @@
         <v>37000</v>
       </c>
       <c r="E83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F83" s="3">
         <v>43000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>60000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>65000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>144000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>385000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>64000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>58000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>144000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>385000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>558000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>421000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>419000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>375000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>553000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>232000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>384000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>328000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>411000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>325000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>307000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>272000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>290000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>272000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>287000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>280000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>258000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>291000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>289000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>279000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>276000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,118 +8845,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-509000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1800000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3287000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1035000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1758000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4864000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>115000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3256000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1876000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4046000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3394000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2632000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-989000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3494000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1525000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1415000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>780000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1935000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>393000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3027000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-696000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3115000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>604000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2243000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1401000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2137000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>873000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>675000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,8 +9001,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8814,8 +9034,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8892,8 +9112,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,118 +9338,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11708000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-980000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7135000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3782000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-220000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-10028000</v>
+      </c>
+      <c r="I94" s="3">
         <v>3443000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2345000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4913000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>13249000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>12707000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3312000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>9022000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>805000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>851000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>162000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,25 +9494,26 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>642000</v>
+      </c>
+      <c r="E96" s="3">
         <v>639000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>644000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>646000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>623000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>624000</v>
       </c>
       <c r="I96" s="3">
         <v>624000</v>
@@ -9289,91 +9522,94 @@
         <v>624000</v>
       </c>
       <c r="K96" s="3">
+        <v>624000</v>
+      </c>
+      <c r="L96" s="3">
         <v>606000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>607000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-612000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-622000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-626000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-531000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-533000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-538000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-492000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-493000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-492000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-494000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-491000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-503000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-509000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-518000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-432000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-436000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-442000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,118 +9944,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2222000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6362000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3870000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2400000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11271000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3619000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1422000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2733000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-796000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>16262000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>68000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4724000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5730000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5196000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3040000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13676000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>26507000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>540000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2893000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9571000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4076000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>538000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>368000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9844,8 +10092,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9922,114 +10170,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8006000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7851000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5065000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1905000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-10456000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-20264000</v>
+      </c>
+      <c r="I102" s="3">
         <v>8820000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3941000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2334000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11190000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>495000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1010000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-432000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-839000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>119000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1269000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>438000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>388000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>291000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2432000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-610000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>255000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>354000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-546000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>360000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>776000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>513000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>36000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>124000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>348000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,259 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5932000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5748000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5407000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5233000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5411000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5189000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5176000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4990000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5129000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5104000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5147000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5368000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5109000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4132000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3281000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="S8" s="3">
-        <v>2975000</v>
       </c>
       <c r="T8" s="3">
         <v>2975000</v>
       </c>
       <c r="U8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="V8" s="3">
         <v>2701000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2483000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2576000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2676000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2855000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3200000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3334000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3503000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3497000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3428000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3348000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1023,47 +1029,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5932000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5748000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5407000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5233000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5411000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5189000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5176000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4990000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5129000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5104000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5147000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5368000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1139,8 +1148,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,8 +1429,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1451,8 +1470,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1529,47 +1548,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E15" s="3">
         <v>101000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>82000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>90000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>164000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>37000</v>
       </c>
       <c r="J15" s="3">
         <v>37000</v>
       </c>
       <c r="K15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="L15" s="3">
         <v>43000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>49000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>60000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>65000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1645,8 +1667,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3603000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3461000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3383000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3387000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3506000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3327000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3357000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3334000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4074000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3245000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3372000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3321000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1833000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>898000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>266000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-98000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-214000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-84000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>422000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-416000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>152000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>192000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>328000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>689000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1067000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1182000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1179000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1142000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>970000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>815000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>724000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>649000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>612000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>586000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>522000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>457000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>384000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2329000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2287000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2024000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1846000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1905000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1862000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1819000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1656000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1055000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1859000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1775000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2047000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3276000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3234000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3015000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3012000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3189000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3059000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2279000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2899000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2424000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2484000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2527000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2511000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2321000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2318000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2286000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2378000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +1990,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1996,202 +2029,208 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-964000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-702000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-670000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-786000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-929000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-885000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-894000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-992000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-763000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2437000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2388000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2106000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1936000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2069000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1883000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1856000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1693000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1098000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1908000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1835000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2112000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1945000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2086000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1980000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2113000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2221000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2234000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1734000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2572000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2307000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1930000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-518000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1207000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1749000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1761000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1731000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1566000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1905000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2228,8 +2267,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2306,240 +2345,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2329000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2287000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2024000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1846000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1905000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1862000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1819000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1656000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1055000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1859000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1775000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2047000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1881000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2028000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1836000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1728000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1663000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1813000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1315000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2197000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1754000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1698000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-902000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>879000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1338000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1436000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1424000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1294000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1615000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E24" s="3">
         <v>465000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>381000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>347000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>278000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>357000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>342000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>312000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>172000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>289000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>275000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>353000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>333000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>388000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>340000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>299000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>357000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>323000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>212000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>371000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>298000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>166000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-158000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>120000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>195000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>255000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>239000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>212000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>264000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>261000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>304000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>253000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>183000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>413000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>386000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>320000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>319000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2033000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1822000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1643000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1499000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1627000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1505000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1477000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1344000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>883000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1570000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1500000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1694000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1548000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1640000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1496000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1429000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1306000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1490000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1103000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1826000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1456000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1532000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-744000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>759000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1143000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1181000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1185000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1082000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1351000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>891000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1922000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1723000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1532000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1399000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1505000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1396000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1355000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1240000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>740000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1440000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1347000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1599000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1401000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1550000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1402000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1355000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1214000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1408000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1037000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1750000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1387000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1447000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-807000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>684000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1061000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1093000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1109000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>999000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>815000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>967000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>975000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3052,8 +3112,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -3064,32 +3124,32 @@
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>4399000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>156000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>238000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>211000</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>189000</v>
       </c>
       <c r="AD29" s="3">
         <v>189000</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>189000</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3100,12 +3160,12 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,8 +3416,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3388,202 +3457,208 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>1395000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1206000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1179000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1284000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1526000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1246000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>964000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>702000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>670000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>786000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3429000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1632000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>929000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>885000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>894000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>992000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>763000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>746000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>701000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>775000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>669000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>670000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>668000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>705000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2020000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1808000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1627000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1481000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1610000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1490000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1459000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1330000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>864000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1554000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1483000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1677000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1401000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1550000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1402000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1355000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1214000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1408000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1037000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1750000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1387000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1447000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3592000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>840000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1299000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1304000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1298000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>967000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>975000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2020000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1808000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1627000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1481000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1610000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1490000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1459000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1330000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>864000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1554000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1483000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1677000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1401000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1550000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1402000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1355000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1214000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1408000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1037000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1750000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1387000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1447000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3592000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>840000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1299000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1304000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1298000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>967000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>975000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,240 +4104,247 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5823000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4710000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4947000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5110000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5936000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5702000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5368000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4999000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5936000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4782000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5604000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5335000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7043000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6548000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8582000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7572000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8004000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8843000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8724000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7455000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7017000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6629000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6338000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7493000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5061000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5671000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5416000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5062000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5608000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8722000</v>
+      </c>
+      <c r="E42" s="3">
         <v>7746000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6129000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5783000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3937000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4083000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3449000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>56821000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4200000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3699000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3811000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>37191000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>27320000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>40278000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>28404000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>48776000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>74250000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>75478000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>72447000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>86161000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>85173000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>70959000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>50233000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19986000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>23413000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>19036000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>18362000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>15261000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10893000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4289,8 +4381,8 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -4367,47 +4459,50 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E44" s="3">
         <v>162000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>33000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>31000</v>
       </c>
       <c r="H44" s="3">
         <v>31000</v>
       </c>
       <c r="I44" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J44" s="3">
         <v>34000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>36000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>35000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>36000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>38000</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
@@ -4483,47 +4578,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1867000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1889000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1860000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1763000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1870000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1881000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2020000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1884000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1925000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1789000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1731000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1692000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4599,47 +4697,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19448000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16454000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15798000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14916000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13592000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13331000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12733000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>65416000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13816000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11746000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12604000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>45859000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4715,129 +4816,135 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>149030000</v>
+      </c>
+      <c r="E47" s="3">
         <v>151495000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>152103000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>147223000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>149332000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>153400000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>147682000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>138740000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>140883000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>140433000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>143676000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>146562000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8437000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8130000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8441000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7798000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8180000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7737000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7521000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6386000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6052000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4938000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4943000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13205000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13734000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13325000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13001000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12567000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12894000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>1692000</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
@@ -4845,32 +4952,32 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3">
         <v>1619000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>1745000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -4890,23 +4997,23 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>1876000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
-        <v>2000000</v>
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB48" s="3">
         <v>2000000</v>
@@ -4915,11 +5022,11 @@
         <v>2000000</v>
       </c>
       <c r="AD48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="AE48" s="3">
         <v>2144000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4929,8 +5036,8 @@
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI48" s="3">
-        <v>0</v>
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ48" s="3">
         <v>0</v>
@@ -4947,124 +5054,130 @@
       <c r="AN48" s="3">
         <v>0</v>
       </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14618000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14589000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14399000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14496000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14643000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14435000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14671000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14694000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14618000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14993000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14442000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14280000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14410000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14193000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13524000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13124000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>12734000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>12718000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12751000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10997000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10475000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10346000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10300000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10315000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10877000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10716000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10848000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11201000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,47 +5411,50 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>61713000</v>
+      </c>
+      <c r="E52" s="3">
         <v>64091000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>54990000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63781000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68871000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>66923000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>64640000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>32224000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>73801000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>76513000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>70461000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33342000</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -5411,8 +5530,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>573572000</v>
+      </c>
+      <c r="E54" s="3">
         <v>568767000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>559107000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>554722000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>560038000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>564881000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>556519000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>566162000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>561580000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>557334000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>558207000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>561777000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>557263000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>559477000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>540786000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>541246000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>557191000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>553515000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>554212000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>474414000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>466679000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>461817000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>458978000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>445493000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>410295000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>408916000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>405761000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>392837000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>382315000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,47 +5856,48 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>440866000</v>
+      </c>
+      <c r="E57" s="3">
         <v>432749000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>426696000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>422915000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>426738000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>423966000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>416391000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>425624000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>421418000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>423609000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>427489000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>436833000</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -5843,47 +5973,50 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2118000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1732000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2053000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2375000</v>
       </c>
-      <c r="G58" s="3">
-        <v>3569000</v>
-      </c>
       <c r="H58" s="3">
+        <v>3168000</v>
+      </c>
+      <c r="I58" s="3">
         <v>2360000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3706000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3922000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3538000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5225000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4565000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3687000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5959,8 +6092,11 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5976,20 +6112,20 @@
       <c r="G59" s="3">
         <v>200000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3">
         <v>200000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
-        <v>200000</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>200000</v>
@@ -5998,124 +6134,127 @@
         <v>200000</v>
       </c>
       <c r="O59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="P59" s="3">
         <v>15762000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19245000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15622000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14623000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12741000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14199000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11186000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11931000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9514000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10629000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12345000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17150000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11831000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12220000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13804000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12793000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9002000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>450077000</v>
+      </c>
+      <c r="E60" s="3">
         <v>443510000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>437269000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>433975000</v>
       </c>
-      <c r="G60" s="3">
-        <v>438808000</v>
-      </c>
       <c r="H60" s="3">
+        <v>438407000</v>
+      </c>
+      <c r="I60" s="3">
         <v>437958000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>429330000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>439209000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>432541000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>438546000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>440414000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>448809000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6191,163 +6330,169 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58641000</v>
+      </c>
+      <c r="E61" s="3">
         <v>62344000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>60424000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>60722000</v>
       </c>
-      <c r="G61" s="3">
-        <v>63142000</v>
-      </c>
       <c r="H61" s="3">
+        <v>63543000</v>
+      </c>
+      <c r="I61" s="3">
         <v>68069000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>71391000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>72707000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>74735000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>66167000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>65384000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>60822000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26638000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24558000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25984000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>26571000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30784000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33471000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>34813000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31530000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33695000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>36610000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>38526000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>49908000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>43922000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>39453000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>39649000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>39468000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35918000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4218000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3875000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3759000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3574000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3619000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3125000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3117000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2872000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3163000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3140000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3063000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3072000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6423,8 +6568,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>512936000</v>
+      </c>
+      <c r="E66" s="3">
         <v>509729000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>501452000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>498271000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>505569000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>509152000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>503838000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>514788000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>510439000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>507853000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>508861000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>512703000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>511489000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>512789000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>493134000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>492065000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>501496000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>497256000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>499585000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>420565000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>412669000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>408541000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>406055000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>396230000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>360981000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>359496000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>356421000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>344301000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>334587000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,47 +7325,50 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>5758000</v>
+      </c>
+      <c r="E70" s="3">
         <v>5755000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>5753000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>5751000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>5749000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>6247000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>6245000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>6243000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>6241000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>7239000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>7237000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>7235000</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>63266000</v>
+      </c>
+      <c r="E72" s="3">
         <v>62008000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>60951000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>60051000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>59282000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58412000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57652000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56913000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>56290000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56170000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>55346000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>54598000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53572000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52777000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>51841000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>51058000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>50228000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>49541000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>48663000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>48113000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>46848000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>45947000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>44986000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>41885000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>42215000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>41413000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>40616000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>39742000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>38919000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>54827000</v>
+      </c>
+      <c r="E76" s="3">
         <v>53235000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51854000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>50654000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48676000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>49442000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46397000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45097000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44864000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42215000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>42083000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41809000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45774000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46688000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47652000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49181000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>55695000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>56259000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>54627000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53849000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>54010000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>53276000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>52923000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>49263000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>49314000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>49420000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>49340000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>48536000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>47728000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2020000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1808000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1627000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1481000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1610000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1490000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1459000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1330000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>864000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1554000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1483000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1677000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1401000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1550000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1402000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1355000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1214000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1408000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1037000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1750000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1387000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1447000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3592000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>840000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1299000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1304000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1298000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>967000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>975000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,124 +8565,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E83" s="3">
         <v>21000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>37000</v>
       </c>
       <c r="F83" s="3">
         <v>37000</v>
       </c>
       <c r="G83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="H83" s="3">
         <v>43000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>49000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>60000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>65000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>64000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>58000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>144000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>385000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>58000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>144000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>385000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>558000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>421000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>419000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>375000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>553000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>232000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>384000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>328000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>411000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>325000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>307000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>272000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>290000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>272000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>287000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>280000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>258000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>291000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>289000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>279000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>276000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>757000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2656000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1480000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-509000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1800000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3287000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1035000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1758000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4864000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>115000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3256000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1876000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4046000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3394000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2632000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-989000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3494000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1525000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1415000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>780000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1935000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>393000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3027000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-696000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3115000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>604000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2243000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1401000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2137000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>873000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>675000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,8 +9441,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9260,8 +9480,8 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -9338,8 +9558,11 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2109000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-820000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11708000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-980000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>7135000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3782000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10028000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3443000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2345000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4913000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>13249000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>12707000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3312000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>9022000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>805000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>851000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>162000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,31 +9960,32 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>676000</v>
+      </c>
+      <c r="E96" s="3">
         <v>678000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>642000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>639000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>644000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>646000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>623000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>624000</v>
       </c>
       <c r="K96" s="3">
         <v>624000</v>
@@ -9761,91 +9994,94 @@
         <v>624000</v>
       </c>
       <c r="M96" s="3">
+        <v>624000</v>
+      </c>
+      <c r="N96" s="3">
         <v>606000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>607000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-612000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-622000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-626000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-531000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-533000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-538000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-492000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-493000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-492000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-494000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-491000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-503000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-509000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-518000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-432000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-436000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-442000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,124 +10434,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2194000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6641000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2222000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6362000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3870000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2400000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11271000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3619000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1422000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2733000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-796000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>16262000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>68000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4724000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5730000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5196000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3040000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>13676000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>26507000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>540000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2893000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>9571000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4076000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>538000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>368000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10346,8 +10594,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10424,120 +10672,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>842000</v>
+      </c>
+      <c r="E102" s="3">
         <v>8477000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8006000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7851000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5065000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1905000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20264000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8820000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3941000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2334000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11190000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>495000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1010000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-432000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-839000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>119000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1269000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>438000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>388000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>291000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2432000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-610000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>255000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>354000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-546000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>360000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>776000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>513000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>36000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>124000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>348000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>335000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,265 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5955000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5932000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5748000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5407000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5233000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5411000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5189000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5176000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4990000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5129000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5104000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5147000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5368000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5109000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4132000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3281000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="T8" s="3">
-        <v>2975000</v>
       </c>
       <c r="U8" s="3">
         <v>2975000</v>
       </c>
       <c r="V8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="W8" s="3">
         <v>2701000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2483000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2576000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2676000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2855000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3200000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3334000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3503000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3497000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3428000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3348000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1032,50 +1038,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5955000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5932000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5748000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5407000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5233000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5411000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5189000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5176000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4990000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5129000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5104000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5147000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5368000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1151,8 +1160,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,8 +1448,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1473,8 +1492,8 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1551,50 +1570,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E15" s="3">
         <v>108000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>101000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>82000</v>
       </c>
-      <c r="G15" s="3">
-        <v>90000</v>
-      </c>
       <c r="H15" s="3">
+        <v>145000</v>
+      </c>
+      <c r="I15" s="3">
         <v>164000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>37000</v>
       </c>
       <c r="K15" s="3">
         <v>37000</v>
       </c>
       <c r="L15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="M15" s="3">
         <v>43000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>49000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>60000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>65000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1670,8 +1692,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3768000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3603000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3461000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3383000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3387000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3506000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3327000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3357000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3334000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4074000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3245000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3372000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3321000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1833000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>898000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>266000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-98000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-214000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-84000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>422000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-416000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>152000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>192000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>328000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>689000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1067000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1182000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1179000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1142000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>970000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>815000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>724000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>649000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>612000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>586000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>522000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>457000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>384000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2187000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2329000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2287000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2024000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1846000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1905000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1862000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1819000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1656000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1055000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1859000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1775000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2047000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3276000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3234000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3015000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3012000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3189000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3059000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2279000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2899000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2424000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2484000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2527000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2511000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2321000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2318000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2286000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2378000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,8 +2023,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,205 +2065,211 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-964000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-702000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-670000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-786000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-929000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-885000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-894000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-992000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-763000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2437000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2388000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2106000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1936000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1991000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2069000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1883000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1856000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1693000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1098000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1908000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1835000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2112000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1945000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2086000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1980000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2113000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2221000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2234000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1734000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2572000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2307000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1930000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-518000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1207000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1749000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1761000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1731000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1566000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1905000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2270,8 +2309,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2348,246 +2387,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2187000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2329000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2287000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2024000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1846000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1905000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1862000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1819000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1656000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1055000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1859000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1775000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2047000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1881000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2028000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1836000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1728000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1663000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1813000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1315000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2197000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1754000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1698000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-902000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>879000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1338000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1436000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1424000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1294000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1615000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E24" s="3">
         <v>296000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>465000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>381000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>347000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>278000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>357000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>342000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>312000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>172000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>289000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>275000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>353000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>333000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>388000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>340000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>299000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>357000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>323000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>212000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>371000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>298000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>166000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-158000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>120000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>195000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>255000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>239000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>212000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>264000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>261000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>304000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>253000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>183000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>413000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>386000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>320000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>319000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1772000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2033000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1822000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1643000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1499000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1627000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1505000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1477000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1344000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>883000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1570000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1500000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1694000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1640000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1496000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1429000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1306000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1490000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1103000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1826000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1456000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1532000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-744000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>759000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1143000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1181000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1185000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1082000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1351000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>891000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1675000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1922000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1723000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1532000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1399000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1505000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1396000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1355000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1240000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>740000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1440000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1347000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1599000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1401000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1550000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1402000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1355000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1214000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1408000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1037000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1750000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1447000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-807000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>684000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1061000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1093000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1109000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>999000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1276000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>815000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>967000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>975000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3115,8 +3175,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
@@ -3127,32 +3187,32 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>4399000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>156000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>238000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>211000</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>189000</v>
       </c>
       <c r="AE29" s="3">
         <v>189000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
+      <c r="AF29" s="3">
+        <v>189000</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
@@ -3163,12 +3223,12 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3181,8 +3241,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,8 +3485,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3460,205 +3529,211 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1395000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1206000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1179000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1284000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1526000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1246000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>964000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>702000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>670000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>786000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3429000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1632000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>929000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>885000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>894000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>992000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>763000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>746000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>701000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>775000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>669000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>670000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>668000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>705000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1760000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2020000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1808000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1627000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1481000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1610000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1490000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1459000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1330000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>864000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1554000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1483000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1677000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1401000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1550000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1402000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1355000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1214000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1408000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1037000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1750000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1447000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3592000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>840000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1299000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1304000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1298000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1276000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>967000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>975000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1760000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2020000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1808000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1627000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1481000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1610000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1490000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1459000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1330000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>864000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1554000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1483000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1677000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1401000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1550000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1402000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1355000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1214000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1408000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1037000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1750000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1447000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3592000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>840000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1299000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1304000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1298000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1276000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>967000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>975000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,246 +4190,253 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5823000</v>
+        <v>5434000</v>
       </c>
       <c r="E41" s="3">
-        <v>4710000</v>
+        <v>6759000</v>
       </c>
       <c r="F41" s="3">
+        <v>5328000</v>
+      </c>
+      <c r="G41" s="3">
         <v>4947000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5110000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>6283000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5702000</v>
+      </c>
+      <c r="K41" s="3">
+        <v>5368000</v>
+      </c>
+      <c r="L41" s="3">
+        <v>4999000</v>
+      </c>
+      <c r="M41" s="3">
         <v>5936000</v>
       </c>
-      <c r="I41" s="3">
-        <v>5702000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>5368000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>4999000</v>
-      </c>
-      <c r="L41" s="3">
-        <v>5936000</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4782000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5604000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5335000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7043000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6548000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8582000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7572000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8004000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8843000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8724000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7455000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7017000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6629000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6338000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7493000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5061000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5671000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5416000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5062000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5608000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8722000</v>
+        <v>8488000</v>
       </c>
       <c r="E42" s="3">
-        <v>7746000</v>
+        <v>7786000</v>
       </c>
       <c r="F42" s="3">
+        <v>7128000</v>
+      </c>
+      <c r="G42" s="3">
         <v>6129000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5783000</v>
       </c>
-      <c r="H42" s="3">
-        <v>3937000</v>
-      </c>
       <c r="I42" s="3">
+        <v>3590000</v>
+      </c>
+      <c r="J42" s="3">
         <v>4083000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3449000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>56821000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4200000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3699000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3811000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>37191000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>27320000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>40278000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>28404000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>48776000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>74250000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>75478000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>72447000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>86161000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>85173000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>70959000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>50233000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>19986000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>23413000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>19036000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>18362000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>15261000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10893000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4384,8 +4476,8 @@
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -4462,50 +4554,53 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E44" s="3">
         <v>143000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>162000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>33000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>31000</v>
       </c>
       <c r="I44" s="3">
         <v>31000</v>
       </c>
       <c r="J44" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K44" s="3">
         <v>34000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>35000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>36000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>35000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>36000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>38000</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -4581,50 +4676,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1878000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1867000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1889000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1860000</v>
       </c>
-      <c r="G45" s="3">
-        <v>1763000</v>
-      </c>
       <c r="H45" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="I45" s="3">
         <v>1870000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1881000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2020000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1884000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1925000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1789000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1731000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1692000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4700,50 +4798,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19448000</v>
+        <v>43536000</v>
       </c>
       <c r="E46" s="3">
-        <v>16454000</v>
+        <v>51448000</v>
       </c>
       <c r="F46" s="3">
+        <v>49154000</v>
+      </c>
+      <c r="G46" s="3">
         <v>15798000</v>
       </c>
-      <c r="G46" s="3">
-        <v>14916000</v>
-      </c>
       <c r="H46" s="3">
-        <v>13592000</v>
+        <v>14453000</v>
       </c>
       <c r="I46" s="3">
+        <v>52592000</v>
+      </c>
+      <c r="J46" s="3">
         <v>13331000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12733000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>65416000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13816000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11746000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12604000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45859000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4819,168 +4920,174 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>153624000</v>
+      </c>
+      <c r="E47" s="3">
         <v>149030000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>151495000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>152103000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>147223000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>149332000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>153400000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>147682000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>138740000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>140883000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>140433000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>143676000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>146562000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8437000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8130000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8441000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7798000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8180000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7737000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7521000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6386000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6052000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4938000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4943000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13205000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13734000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13325000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13001000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12567000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12894000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
         <v>1692000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>1619000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>1745000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -5000,23 +5107,23 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>1876000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
-        <v>2000000</v>
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC48" s="3">
         <v>2000000</v>
@@ -5025,11 +5132,11 @@
         <v>2000000</v>
       </c>
       <c r="AE48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="AF48" s="3">
         <v>2144000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5039,8 +5146,8 @@
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ48" s="3">
-        <v>0</v>
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK48" s="3">
         <v>0</v>
@@ -5057,127 +5164,133 @@
       <c r="AO48" s="3">
         <v>0</v>
       </c>
+      <c r="AP48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17098000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14618000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14589000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14399000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14496000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14643000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14435000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14671000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14694000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14618000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14993000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14442000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14280000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14410000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14193000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13524000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13124000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>12734000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12718000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12751000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10997000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10475000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10346000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10300000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10315000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10877000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10716000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10848000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11201000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,50 +5530,53 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>61713000</v>
+        <v>32510000</v>
       </c>
       <c r="E52" s="3">
-        <v>64091000</v>
+        <v>29713000</v>
       </c>
       <c r="F52" s="3">
+        <v>31391000</v>
+      </c>
+      <c r="G52" s="3">
         <v>54990000</v>
       </c>
-      <c r="G52" s="3">
-        <v>63781000</v>
-      </c>
       <c r="H52" s="3">
-        <v>68871000</v>
+        <v>64244000</v>
       </c>
       <c r="I52" s="3">
+        <v>29871000</v>
+      </c>
+      <c r="J52" s="3">
         <v>66923000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>64640000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32224000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>73801000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>76513000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>70461000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33342000</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -5533,8 +5652,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>603028000</v>
+      </c>
+      <c r="E54" s="3">
         <v>573572000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>568767000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>559107000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>554722000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>560038000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>564881000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>556519000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>566162000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>561580000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>557334000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>558207000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>561777000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>557263000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>559477000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>540786000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>541246000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>557191000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>553515000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>554212000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>474414000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>466679000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>461817000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>458978000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>445493000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>410295000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>408916000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>405761000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>392837000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>382315000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,50 +5986,51 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>457648000</v>
+      </c>
+      <c r="E57" s="3">
         <v>440866000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>432749000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>426696000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>422915000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>426738000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>423966000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>416391000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>425624000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>421418000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>423609000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>427489000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>436833000</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -5976,50 +6106,53 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1822000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2118000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1732000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2053000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2375000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3168000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2360000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3706000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3922000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3538000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5225000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4565000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3687000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6095,13 +6228,16 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>200000</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E59" s="3">
         <v>200000</v>
@@ -6112,23 +6248,23 @@
       <c r="G59" s="3">
         <v>200000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="H59" s="3">
         <v>200000</v>
       </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="J59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="K59" s="3">
         <v>100000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
-        <v>200000</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>200000</v>
@@ -6137,127 +6273,130 @@
         <v>200000</v>
       </c>
       <c r="P59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="Q59" s="3">
         <v>15762000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19245000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15622000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14623000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12741000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14199000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11186000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11931000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9514000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10629000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12345000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17150000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11831000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12220000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13804000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12793000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9002000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>468954000</v>
+      </c>
+      <c r="E60" s="3">
         <v>450077000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>443510000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>437269000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>433975000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>438407000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>437958000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>429330000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>439209000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>432541000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>438546000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>440414000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>448809000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6333,169 +6472,175 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>66666000</v>
+      </c>
+      <c r="E61" s="3">
         <v>58641000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62344000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>60424000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>60722000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>63543000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>68069000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>71391000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>72707000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>74735000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>66167000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>65384000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>60822000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26638000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>24558000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>25984000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>26571000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30784000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33471000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>34813000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>31530000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33695000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>36610000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>38526000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>49908000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>43922000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>39453000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>39649000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>39468000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35918000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3732000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4218000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3875000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3759000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3574000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3619000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3125000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3117000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2872000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3163000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3140000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3063000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3072000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6571,8 +6716,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>539352000</v>
+      </c>
+      <c r="E66" s="3">
         <v>512936000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>509729000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>501452000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>498271000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>505569000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>509152000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>503838000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>514788000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>510439000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>507853000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>508861000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>512703000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>511489000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>512789000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>493134000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>492065000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>501496000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>497256000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>499585000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>420565000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>412669000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>408541000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>406055000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>396230000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>360981000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>359496000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>356421000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>344301000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>334587000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,50 +7492,53 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>5878000</v>
+      </c>
+      <c r="E70" s="3">
         <v>5758000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>5755000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>5753000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>5751000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>5749000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>6247000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>6245000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>6243000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>6241000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>7239000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>7237000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>7235000</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>64256000</v>
+      </c>
+      <c r="E72" s="3">
         <v>63266000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>62008000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>60951000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>60051000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>59282000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>58412000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>57652000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>56913000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56290000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>56170000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>55346000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>54598000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53572000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52777000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>51841000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>51058000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50228000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>49541000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>48663000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>48113000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>46848000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>45947000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>44986000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>41885000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>42215000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>41413000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>40616000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>39742000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>38919000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57749000</v>
+      </c>
+      <c r="E76" s="3">
         <v>54827000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53235000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51854000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50654000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48676000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>49442000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46397000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45097000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44864000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>42215000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>42083000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41809000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45774000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>46688000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47652000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49181000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>55695000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>56259000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>54627000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>53849000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>54010000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>53276000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>52923000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>49263000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>49314000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>49420000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>49340000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>48536000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>47728000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1760000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2020000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1808000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1627000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1481000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1610000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1490000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1459000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1330000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>864000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1554000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1483000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1677000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1401000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1550000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1402000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1355000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1214000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1408000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1037000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1750000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1447000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3592000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>840000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1299000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1304000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1298000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1276000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>967000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>975000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8763,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E83" s="3">
         <v>164000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>37000</v>
       </c>
       <c r="G83" s="3">
         <v>37000</v>
       </c>
       <c r="H83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I83" s="3">
         <v>43000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>49000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>60000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>65000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>64000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>58000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>144000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>385000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>64000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>58000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>144000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>385000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>558000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>421000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>419000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>375000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>553000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>232000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>384000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>328000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>411000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>325000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>307000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>272000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>290000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>272000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>287000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>280000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>258000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>291000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>289000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>279000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>276000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E89" s="3">
         <v>757000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2656000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1480000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-509000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1800000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3287000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1035000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1758000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4864000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>115000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3256000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1876000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4046000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3394000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2632000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-989000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3494000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1525000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1415000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>780000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1935000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>393000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3027000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-696000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3115000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>604000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2243000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1401000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2137000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>873000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>675000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,8 +9661,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9483,8 +9703,8 @@
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9561,8 +9781,11 @@
       <c r="AO91" s="3">
         <v>0</v>
       </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10586000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2109000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-820000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11708000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-980000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>7135000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3782000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10028000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3443000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2345000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4913000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>13249000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>12707000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3312000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>9022000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>805000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>851000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>162000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,34 +10193,35 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>696000</v>
+      </c>
+      <c r="E96" s="3">
         <v>676000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>678000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>642000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>639000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>644000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>646000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>623000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>624000</v>
       </c>
       <c r="L96" s="3">
         <v>624000</v>
@@ -9997,91 +10230,94 @@
         <v>624000</v>
       </c>
       <c r="N96" s="3">
+        <v>624000</v>
+      </c>
+      <c r="O96" s="3">
         <v>606000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>607000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-612000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-622000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-626000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-531000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-533000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-538000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-492000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-493000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-492000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-494000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-491000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-503000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-509000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-518000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-432000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-436000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-442000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,127 +10679,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2194000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6641000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2222000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6362000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3870000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2400000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11271000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3619000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1422000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2733000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-796000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>16262000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>68000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4724000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5730000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5196000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3040000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>13676000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>26507000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>540000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2893000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>9571000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4076000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>538000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>368000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,8 +10845,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10675,123 +10923,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8014000</v>
+      </c>
+      <c r="E102" s="3">
         <v>842000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8477000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8006000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7851000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5065000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1905000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20264000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8820000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3941000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2334000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11190000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>495000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1010000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-432000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-839000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>119000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1269000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>438000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>388000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>291000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2432000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-610000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>255000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>354000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-546000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>360000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>776000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>513000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>36000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>124000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>348000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>335000</v>
       </c>
     </row>
